--- a/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
+++ b/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
@@ -1,34 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B78BC2A-8AB2-4047-9D60-869754027FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D940FCAB-2447-4936-AE42-6005C81BB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="Anotaciones" sheetId="4" r:id="rId3"/>
-    <sheet name="EDESUR" sheetId="3" r:id="rId4"/>
+    <sheet name="EDESUR" sheetId="3" r:id="rId3"/>
+    <sheet name="Anotaciones" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">EDESUR!$B$3:$J$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="146">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -421,70 +426,55 @@
     <t>SUM</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>Transf 06/05</t>
-  </si>
-  <si>
-    <t>Transf 08/05</t>
-  </si>
-  <si>
-    <t>Recarga de matafuegos</t>
-  </si>
-  <si>
-    <t>Transf 05/05</t>
-  </si>
-  <si>
-    <t>Debito 06/05</t>
-  </si>
-  <si>
-    <t>Pintor - Sr. Gabriel - Trabajo en medianeras</t>
-  </si>
-  <si>
-    <t>Transf 07/05</t>
-  </si>
-  <si>
-    <t>Sr. Herrero - Tacho de basura</t>
-  </si>
-  <si>
-    <t>Transf 18/05</t>
-  </si>
-  <si>
-    <t>Lema - Ascensores - Alineacion cabina de ascensores (se desmontan los rodillos, se limpian, se egrasan, retiran y se vuelven a colocar alineadas las cuneas para no ocasionar mas ruido con la cabina al deslizarse desnivelada)</t>
-  </si>
-  <si>
-    <t>Transf 27/05</t>
-  </si>
-  <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 3  - Restan 3 cuotas de $157.988,29</t>
-  </si>
-  <si>
     <t>FCI FIMA</t>
   </si>
   <si>
-    <t>Comision cuenta dolares</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ingreso 05/05 </t>
   </si>
   <si>
-    <t>SALDO TOTAL AL 29/5</t>
-  </si>
-  <si>
-    <t>Egreso a FCI FIMA</t>
-  </si>
-  <si>
-    <t>Honorario administracion - Mes de MAYO - Se transfirieron el 29/05 y no fueron incluidos en extracto bancario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajuste inflacionario de honorarios -  mes anterior no cobrado </t>
-  </si>
-  <si>
-    <t>El mes pasado a la cochera 2 le quedo dinero a favor que correspondia para pagar la cochera 3</t>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Transf 02/06</t>
+  </si>
+  <si>
+    <t>Transf 04/06</t>
+  </si>
+  <si>
+    <t>Cambio de caja de piso</t>
+  </si>
+  <si>
+    <t>Cambio de cierrapuerta de blindex</t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
+  </si>
+  <si>
+    <t>Transf 08/06</t>
+  </si>
+  <si>
+    <t>Horas extra Sra. Carina</t>
+  </si>
+  <si>
+    <t>Transf 16/06</t>
+  </si>
+  <si>
+    <t>Easy Barracas - Compra de termotanque - Cuota 4  - Restan 2 cuotas de $157.988,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorario administracion - Mes de JUNIO </t>
+  </si>
+  <si>
+    <t>Transf 30/06</t>
+  </si>
+  <si>
+    <t>Comision cuenta dolares - Reclamo enviado - El banco evaluara una bonificacion</t>
+  </si>
+  <si>
+    <t>SALDO A FIN DE MES</t>
   </si>
 </sst>
 </file>
@@ -700,7 +690,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -773,12 +763,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1308,9 +1292,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1405,9 +1386,6 @@
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1435,12 +1413,8 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1448,8 +1422,29 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1460,108 +1455,84 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1574,8 +1545,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1654,9 +1638,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1694,9 +1678,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1729,9 +1713,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1764,9 +1765,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1940,22 +1958,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M103"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="49" t="s">
         <v>74</v>
@@ -1964,7 +1982,7 @@
       <c r="D1" s="49"/>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="51" t="s">
         <v>14</v>
@@ -1973,16 +1991,16 @@
       <c r="D2" s="51"/>
       <c r="E2" s="52"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="201"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="193"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -1993,12 +2011,12 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>75</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="51" t="s">
@@ -2006,7 +2024,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>126</v>
       </c>
@@ -2017,57 +2035,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="203" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="203"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="203"/>
-      <c r="C9" s="203"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="203"/>
-      <c r="C10" s="203"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="202" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="195" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="195"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="202"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="202"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
-      <c r="B15" s="202"/>
-      <c r="C15" s="202"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="202"/>
-      <c r="B16" s="202"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="194"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="194"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="194"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>104</v>
       </c>
@@ -2076,7 +2094,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>77</v>
       </c>
@@ -2085,746 +2103,726 @@
       <c r="D21" s="108"/>
       <c r="E21" s="99"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="196" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="190" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="197"/>
+      <c r="B22" s="191"/>
       <c r="C22" s="37"/>
-      <c r="D22" s="183">
+      <c r="D22" s="230">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="176" t="s">
-        <v>131</v>
+      <c r="E22" s="174" t="s">
+        <v>134</v>
       </c>
       <c r="H22" s="88"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="196"/>
-      <c r="B23" s="197"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="190" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="191"/>
       <c r="C23" s="37"/>
-      <c r="D23" s="183"/>
+      <c r="D23" s="230">
+        <v>15000</v>
+      </c>
       <c r="E23" s="102"/>
       <c r="H23" s="88"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="166">
+      <c r="D24" s="181"/>
+      <c r="E24" s="164">
         <f>SUM(D22:D23)</f>
-        <v>510846.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>525846.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="167"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="196" t="s">
+      <c r="D25" s="182"/>
+      <c r="E25" s="165"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="190" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="197"/>
+      <c r="B26" s="191"/>
       <c r="C26" s="39"/>
-      <c r="D26" s="186">
-        <v>75267</v>
-      </c>
-      <c r="E26" s="165" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D26" s="232">
+        <v>79864</v>
+      </c>
+      <c r="E26" s="104" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="118">
+      <c r="D27" s="181"/>
+      <c r="E27" s="117">
         <f>SUM(D26:D26)</f>
-        <v>75267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>79864</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="100"/>
       <c r="C28" s="100"/>
-      <c r="D28" s="187"/>
-      <c r="E28" s="168"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="183"/>
+      <c r="E28" s="166"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="188">
-        <v>0</v>
-      </c>
-      <c r="E29" s="176"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="184">
+        <v>0</v>
+      </c>
+      <c r="E29" s="174"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="188">
-        <v>6420.51</v>
-      </c>
-      <c r="E30" s="176" t="str">
+      <c r="D30" s="229">
+        <v>6403.1</v>
+      </c>
+      <c r="E30" s="174" t="str">
         <f>E31</f>
-        <v>Transf 05/05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Transf 02/06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B31" s="115"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="188">
-        <v>330512.58</v>
+      <c r="D31" s="229">
+        <v>329815.06</v>
       </c>
       <c r="E31" s="104" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="198" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="199"/>
+      <c r="B32" s="189"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="188">
-        <v>193996.95</v>
+      <c r="D32" s="229">
+        <v>640644</v>
       </c>
       <c r="E32" s="104" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="105" t="s">
         <v>78</v>
       </c>
       <c r="B33" s="101"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="188">
-        <v>24915.01</v>
+      <c r="D33" s="229">
+        <v>26036.19</v>
       </c>
       <c r="E33" s="104" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="189"/>
-      <c r="E34" s="169">
+      <c r="D34" s="185"/>
+      <c r="E34" s="167">
         <f>SUM(D29:D33)</f>
-        <v>555845.05000000005</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1002898.3499999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="170"/>
-    </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="196" t="s">
+      <c r="D35" s="181"/>
+      <c r="E35" s="168"/>
+    </row>
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="190" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="197"/>
+      <c r="B36" s="191"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="188">
+      <c r="D36" s="229">
         <v>82000</v>
       </c>
       <c r="E36" s="104" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="B37" s="197"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="173" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="116"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="190">
-        <v>300000</v>
+      <c r="D37" s="231">
+        <v>150000</v>
       </c>
       <c r="E37" s="104" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="190" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="191"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="231">
+        <v>500000</v>
+      </c>
+      <c r="E38" s="104" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="190" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" s="117"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="190">
-        <v>900000</v>
-      </c>
-      <c r="E38" s="104" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="196" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="197"/>
+      <c r="B39" s="191"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="190">
-        <v>148155</v>
-      </c>
-      <c r="E39" s="104" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="116" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="117"/>
+      <c r="D39" s="231">
+        <v>157988.29</v>
+      </c>
+      <c r="E39" s="104"/>
+    </row>
+    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="190"/>
+      <c r="B40" s="191"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="190">
-        <v>120000</v>
-      </c>
-      <c r="E40" s="104" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="196" t="s">
+      <c r="D40" s="186"/>
+      <c r="E40" s="104"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="117">
+        <f>SUM(D36:D40)</f>
+        <v>889988.29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="169"/>
+    </row>
+    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="190" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="197"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="190">
-        <v>157988.29</v>
-      </c>
-      <c r="E41" s="104"/>
-    </row>
-    <row r="42" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="196"/>
-      <c r="B42" s="197"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="190"/>
-      <c r="E42" s="104"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="118">
-        <f>SUM(D36:D42)</f>
-        <v>1708143.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="191"/>
-      <c r="E44" s="171"/>
-    </row>
-    <row r="45" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="196" t="s">
-        <v>148</v>
-      </c>
-      <c r="B45" s="197"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="192">
+      <c r="B43" s="191"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="233">
         <v>170000</v>
       </c>
-      <c r="E45" s="172"/>
-    </row>
-    <row r="46" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="196" t="s">
-        <v>149</v>
-      </c>
-      <c r="B46" s="197"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="192">
-        <v>20000</v>
-      </c>
-      <c r="E46" s="172"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="s">
+      <c r="E43" s="170" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="109"/>
-      <c r="E47" s="166">
-        <f>SUM(D45:D46)</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="109"/>
+      <c r="E44" s="164">
+        <f>SUM(D43:D43)</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="107"/>
-      <c r="E48" s="118"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="B45" s="47"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="107"/>
+      <c r="E45" s="117"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="103">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="229">
         <v>69000</v>
       </c>
-      <c r="E49" s="173"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="E46" s="171"/>
+    </row>
+    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="234" t="s">
         <v>144</v>
       </c>
+      <c r="B47" s="235"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="229">
+        <v>14770</v>
+      </c>
+      <c r="E47" s="171"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="229">
+        <v>56522.84</v>
+      </c>
+      <c r="E48" s="172"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="117">
+        <f>SUM(D46:D48)</f>
+        <v>140292.84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="103">
-        <v>14125</v>
-      </c>
-      <c r="E50" s="173"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="103">
-        <f>66953.59-6952+140+10-6798</f>
-        <v>53353.59</v>
-      </c>
-      <c r="E51" s="174"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="118">
-        <f>SUM(D49:D51)</f>
-        <v>136478.59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="76"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="22" t="s">
+      <c r="D50" s="70"/>
+      <c r="E50" s="76"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="119"/>
-    </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="118"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="29"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="8"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="81">
+        <f>(SUM(E21:E51))</f>
+        <v>2808890.3299999996</v>
+      </c>
+      <c r="F53" s="98"/>
+      <c r="G53" s="29"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D54" s="78"/>
+      <c r="E54" s="78"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D55" s="78"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="29"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="81">
-        <f>(SUM(E21:E54))</f>
-        <v>3176580.78</v>
-      </c>
-      <c r="F56" s="98"/>
-      <c r="G56" s="29"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-    </row>
-    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D58" s="78"/>
-      <c r="E58" s="78"/>
-      <c r="H58" s="110"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
+      <c r="E55" s="78"/>
+      <c r="H55" s="110"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="83"/>
-    </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="10"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="83"/>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="72"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="71"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="198"/>
+      <c r="B58" s="198"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="103"/>
+      <c r="E58" s="71"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="72"/>
-      <c r="B60" s="101"/>
+      <c r="B60" s="74"/>
       <c r="C60" s="5"/>
       <c r="D60" s="73"/>
       <c r="E60" s="71"/>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="195"/>
-      <c r="B61" s="195"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="103"/>
-      <c r="E61" s="71"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="72"/>
-      <c r="B63" s="74"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="73"/>
-      <c r="E63" s="71"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="34"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40">
-        <f>SUM(D60:D63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="22" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40">
+        <f>SUM(D57:D60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="162"/>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="161"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="48">
-        <f>E64+E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="8"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="48">
+        <f>E61+E64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" s="69">
+        <f>E53</f>
+        <v>2808890.3299999996</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="69">
+        <f>E53-E51</f>
+        <v>2808890.3299999996</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="69">
+        <f>E66-E64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="68" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B71" s="69">
-        <f>E56</f>
-        <v>3176580.78</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="68" t="s">
-        <v>106</v>
-      </c>
-      <c r="B72" s="69">
-        <f>E56-E54</f>
-        <v>3176580.78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="68" t="s">
-        <v>107</v>
-      </c>
-      <c r="B73" s="69">
-        <f>E69-E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="B74" s="69">
-        <f>E69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="26"/>
-    </row>
-    <row r="77" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="90" t="s">
+        <f>E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="26"/>
+    </row>
+    <row r="74" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="129">
-        <v>956980.3900000006</v>
-      </c>
-      <c r="C77" s="26"/>
-      <c r="D77" s="32"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="39" t="s">
+      <c r="B74" s="128">
+        <v>291888.99000000162</v>
+      </c>
+      <c r="C74" s="26"/>
+      <c r="D74" s="32"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B78" s="95">
-        <f>-B72</f>
-        <v>-3176580.78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="39" t="s">
+      <c r="B75" s="95">
+        <f>-B69</f>
+        <v>-2808890.3299999996</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B79" s="95">
-        <f>B102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="39" t="s">
+      <c r="B76" s="95">
+        <f>B98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B80" s="96">
-        <f>PRORRATEO!G36-B87</f>
-        <v>2511489.3800000008</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="97" t="s">
+      <c r="B77" s="96">
+        <f>PRORRATEO!G36-B84</f>
+        <v>2367966.9600000004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="111"/>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="93" t="s">
+      <c r="B78" s="111"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="B82" s="94">
-        <f>SUM(B77:C81)</f>
-        <v>291888.99000000162</v>
+      <c r="B79" s="94">
+        <f>SUM(B74:C78)</f>
+        <v>-149034.37999999756</v>
+      </c>
+      <c r="D79" s="29"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="91"/>
+      <c r="B80" s="91"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="28"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="128">
+        <v>1000000</v>
+      </c>
+      <c r="D81" s="28"/>
+      <c r="E81" s="29"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" s="95">
+        <f>-B70</f>
+        <v>0</v>
       </c>
       <c r="D82" s="29"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="91"/>
-      <c r="B83" s="91"/>
+      <c r="E82" s="29"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" s="95">
+        <f>B106</f>
+        <v>0</v>
+      </c>
       <c r="D83" s="29"/>
-      <c r="E83" s="28"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="90" t="s">
-        <v>110</v>
-      </c>
-      <c r="B84" s="129">
-        <v>2000000</v>
-      </c>
-      <c r="D84" s="28"/>
-      <c r="E84" s="29"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="95">
-        <f>-B73</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B86" s="95">
-        <f>B110</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="29"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="39" t="s">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B87" s="96">
-        <v>0</v>
-      </c>
-      <c r="D87" s="163"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="B88" s="96">
-        <v>-1000000</v>
-      </c>
-      <c r="D88" s="163"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="97" t="s">
+      <c r="B84" s="96">
+        <v>0</v>
+      </c>
+      <c r="D84" s="162"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B89" s="111"/>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="93" t="s">
+      <c r="B85" s="111"/>
+      <c r="E85" s="29">
+        <f>B86+B79</f>
+        <v>850965.62000000244</v>
+      </c>
+      <c r="F85">
+        <f>1006974.16-20000</f>
+        <v>986974.16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="B90" s="94">
-        <f>SUM(B84:C89)</f>
+      <c r="B86" s="94">
+        <f>SUM(B81:C85)</f>
         <v>1000000</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="91"/>
-      <c r="B91" s="91"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="91"/>
-      <c r="B92" s="91"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="90" t="s">
-        <v>143</v>
-      </c>
-      <c r="B93" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="39" t="s">
+      <c r="F86" s="29">
+        <f>F85-E85</f>
+        <v>136008.53999999759</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="91"/>
+      <c r="B87" s="91"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="91"/>
+      <c r="B88" s="91"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89" s="128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90" s="95">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="97"/>
+      <c r="B91" s="111"/>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="93" t="s">
         <v>145</v>
       </c>
-      <c r="B94" s="95">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="97"/>
-      <c r="B95" s="111"/>
-    </row>
-    <row r="96" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="93" t="s">
-        <v>146</v>
-      </c>
-      <c r="B96" s="94">
-        <v>1010500.1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="194" t="s">
+      <c r="B92" s="94">
+        <v>1025063.51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="197" t="s">
         <v>18</v>
       </c>
-      <c r="B98" s="194"/>
-      <c r="C98" s="194"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="194"/>
-      <c r="B99" s="194"/>
-      <c r="C99" s="194"/>
-    </row>
-    <row r="100" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="85"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25">
+      <c r="B94" s="197"/>
+      <c r="C94" s="197"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="197"/>
+      <c r="B95" s="197"/>
+      <c r="C95" s="197"/>
+    </row>
+    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="85"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25">
         <v>40000</v>
       </c>
-      <c r="E100" s="98"/>
-    </row>
-    <row r="101" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="85"/>
-      <c r="B101" s="87"/>
-      <c r="C101" s="84"/>
-      <c r="D101" s="98"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="30" t="s">
+      <c r="E96" s="98"/>
+    </row>
+    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="85"/>
+      <c r="B97" s="87"/>
+      <c r="C97" s="84"/>
+      <c r="D97" s="98"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B102" s="86">
-        <f>SUM(B100:B101)</f>
-        <v>0</v>
-      </c>
-      <c r="C102" s="31"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M103" s="6"/>
-    </row>
-    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="193"/>
-      <c r="B104" s="193"/>
-      <c r="C104" s="193"/>
-      <c r="D104" s="193"/>
-      <c r="E104" s="193"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="193"/>
-      <c r="B105" s="193"/>
-      <c r="C105" s="193"/>
-      <c r="D105" s="193"/>
-      <c r="E105" s="193"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="193"/>
-      <c r="B106" s="193"/>
-      <c r="C106" s="193"/>
-      <c r="D106" s="193"/>
-      <c r="E106" s="193"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="193"/>
-      <c r="B107" s="193"/>
-      <c r="C107" s="193"/>
-      <c r="D107" s="193"/>
-      <c r="E107" s="193"/>
+      <c r="B98" s="86">
+        <f>SUM(B96:B97)</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="31"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M99" s="6"/>
+    </row>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="196"/>
+      <c r="B100" s="196"/>
+      <c r="C100" s="196"/>
+      <c r="D100" s="196"/>
+      <c r="E100" s="196"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="196"/>
+      <c r="B101" s="196"/>
+      <c r="C101" s="196"/>
+      <c r="D101" s="196"/>
+      <c r="E101" s="196"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="196"/>
+      <c r="B102" s="196"/>
+      <c r="C102" s="196"/>
+      <c r="D102" s="196"/>
+      <c r="E102" s="196"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="196"/>
+      <c r="B103" s="196"/>
+      <c r="C103" s="196"/>
+      <c r="D103" s="196"/>
+      <c r="E103" s="196"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
+    <mergeCell ref="A100:E103"/>
+    <mergeCell ref="A94:C95"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2832,16 +2830,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A104:E107"/>
-    <mergeCell ref="A98:C99"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2852,229 +2840,229 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130"/>
-      <c r="B1" s="131"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="209"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="133"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="134"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137" t="s">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="132"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="137"/>
-      <c r="G2" s="138">
-        <v>0</v>
-      </c>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137" t="s">
+      <c r="F2" s="136"/>
+      <c r="G2" s="137">
+        <v>0</v>
+      </c>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="139">
+      <c r="K2" s="138">
         <v>2400000</v>
       </c>
-      <c r="L2" s="139"/>
-      <c r="M2" s="139"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="142"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="141"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="134"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="140"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="142"/>
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="133"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="139"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="141"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="216" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="210" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="217"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="218"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="212"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="219"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="M5" s="220"/>
-      <c r="N5" s="220"/>
-      <c r="O5" s="220"/>
-      <c r="P5" s="221"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="213"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="214"/>
+      <c r="F5" s="214"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="214"/>
+      <c r="L5" s="214"/>
+      <c r="M5" s="214"/>
+      <c r="N5" s="214"/>
+      <c r="O5" s="214"/>
+      <c r="P5" s="215"/>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="219"/>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="220"/>
-      <c r="H6" s="220"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="220"/>
-      <c r="L6" s="220"/>
-      <c r="M6" s="220"/>
-      <c r="N6" s="220"/>
-      <c r="O6" s="220"/>
-      <c r="P6" s="221"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="213"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="214"/>
+      <c r="F6" s="214"/>
+      <c r="G6" s="214"/>
+      <c r="H6" s="214"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="214"/>
+      <c r="K6" s="214"/>
+      <c r="L6" s="214"/>
+      <c r="M6" s="214"/>
+      <c r="N6" s="214"/>
+      <c r="O6" s="214"/>
+      <c r="P6" s="215"/>
       <c r="Q6" s="20"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="219"/>
-      <c r="B7" s="220"/>
-      <c r="C7" s="220"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="220"/>
-      <c r="F7" s="220"/>
-      <c r="G7" s="220"/>
-      <c r="H7" s="220"/>
-      <c r="I7" s="220"/>
-      <c r="J7" s="220"/>
-      <c r="K7" s="220"/>
-      <c r="L7" s="220"/>
-      <c r="M7" s="220"/>
-      <c r="N7" s="220"/>
-      <c r="O7" s="220"/>
-      <c r="P7" s="221"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="213"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="214"/>
+      <c r="D7" s="214"/>
+      <c r="E7" s="214"/>
+      <c r="F7" s="214"/>
+      <c r="G7" s="214"/>
+      <c r="H7" s="214"/>
+      <c r="I7" s="214"/>
+      <c r="J7" s="214"/>
+      <c r="K7" s="214"/>
+      <c r="L7" s="214"/>
+      <c r="M7" s="214"/>
+      <c r="N7" s="214"/>
+      <c r="O7" s="214"/>
+      <c r="P7" s="215"/>
       <c r="Q7" s="20"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="222"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
-      <c r="K8" s="223"/>
-      <c r="L8" s="223"/>
-      <c r="M8" s="223"/>
-      <c r="N8" s="223"/>
-      <c r="O8" s="223"/>
-      <c r="P8" s="224"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="227" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="216"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="217"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="217"/>
+      <c r="J8" s="217"/>
+      <c r="K8" s="217"/>
+      <c r="L8" s="217"/>
+      <c r="M8" s="217"/>
+      <c r="N8" s="217"/>
+      <c r="O8" s="217"/>
+      <c r="P8" s="218"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="228"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="228"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="228"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="228"/>
-      <c r="J9" s="228"/>
-      <c r="K9" s="228"/>
-      <c r="L9" s="228"/>
-      <c r="M9" s="228"/>
-      <c r="N9" s="228"/>
-      <c r="O9" s="228"/>
-      <c r="P9" s="228"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="229" t="s">
+      <c r="B9" s="222"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
+      <c r="M9" s="222"/>
+      <c r="N9" s="222"/>
+      <c r="O9" s="222"/>
+      <c r="P9" s="222"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="223" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="229"/>
-      <c r="C10" s="229"/>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="229"/>
-      <c r="I10" s="229"/>
-      <c r="J10" s="229"/>
-      <c r="K10" s="229"/>
-      <c r="L10" s="229"/>
-      <c r="M10" s="229"/>
-      <c r="N10" s="229"/>
-      <c r="O10" s="229"/>
-      <c r="P10" s="229"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="223"/>
+      <c r="I10" s="223"/>
+      <c r="J10" s="223"/>
+      <c r="K10" s="223"/>
+      <c r="L10" s="223"/>
+      <c r="M10" s="223"/>
+      <c r="N10" s="223"/>
+      <c r="O10" s="223"/>
+      <c r="P10" s="223"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="204" t="s">
         <v>3</v>
       </c>
@@ -3088,62 +3076,62 @@
       <c r="E11" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="207" t="s">
+      <c r="F11" s="200" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="212" t="s">
+      <c r="H11" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="207" t="s">
+      <c r="I11" s="200" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="207" t="s">
+      <c r="J11" s="200" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="214" t="s">
+      <c r="K11" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="207" t="s">
+      <c r="L11" s="200" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="207" t="s">
+      <c r="M11" s="200" t="s">
         <v>128</v>
       </c>
       <c r="N11" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="210" t="s">
+      <c r="O11" s="202" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="225" t="s">
+      <c r="P11" s="219" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="206"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="205"/>
       <c r="B12" s="113"/>
-      <c r="C12" s="206"/>
-      <c r="D12" s="205"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="208"/>
-      <c r="G12" s="206"/>
-      <c r="H12" s="213"/>
-      <c r="I12" s="208"/>
-      <c r="J12" s="208"/>
-      <c r="K12" s="215"/>
-      <c r="L12" s="208"/>
-      <c r="M12" s="208"/>
+      <c r="C12" s="205"/>
+      <c r="D12" s="224"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="205"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="201"/>
+      <c r="K12" s="209"/>
+      <c r="L12" s="201"/>
+      <c r="M12" s="201"/>
       <c r="N12" s="41" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="O12" s="211"/>
-      <c r="P12" s="226"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>VTO 17/07</v>
+      </c>
+      <c r="O12" s="203"/>
+      <c r="P12" s="220"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44">
         <v>1</v>
       </c>
@@ -3158,19 +3146,19 @@
         <v>12</v>
       </c>
       <c r="F13" s="54">
-        <v>264000.01</v>
+        <v>288000.01</v>
       </c>
       <c r="G13" s="55">
-        <f>F13</f>
-        <v>264000.01</v>
+        <f>316800.01+396-G29-G30</f>
+        <v>287999.66000000003</v>
       </c>
       <c r="H13" s="56">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>0</v>
+        <v>0.34999999997671694</v>
       </c>
       <c r="I13" s="56">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>0</v>
+        <v>1.0499999999301507E-2</v>
       </c>
       <c r="J13" s="106">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
@@ -3180,12 +3168,12 @@
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="161">
+      <c r="L13" s="160">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="178"/>
-      <c r="N13" s="160">
+      <c r="M13" s="176"/>
+      <c r="N13" s="159">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
         <v>288000.01</v>
       </c>
@@ -3201,65 +3189,65 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="153">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="152">
         <v>2</v>
       </c>
-      <c r="B14" s="153" t="s">
+      <c r="B14" s="152" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="155">
+      <c r="D14" s="153"/>
+      <c r="E14" s="154">
         <v>6.6</v>
       </c>
       <c r="F14" s="55">
-        <v>179889.02</v>
+        <v>189415.02</v>
       </c>
       <c r="G14" s="55">
-        <v>180000</v>
-      </c>
-      <c r="H14" s="156">
+        <v>190000</v>
+      </c>
+      <c r="H14" s="155">
         <f t="shared" si="0"/>
-        <v>-110.98000000001048</v>
-      </c>
-      <c r="I14" s="156">
+        <v>-584.98000000001048</v>
+      </c>
+      <c r="I14" s="155">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="156">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="164">
+      <c r="L14" s="163">
         <f>EDESUR!I6</f>
-        <v>31125.624497318255</v>
-      </c>
-      <c r="M14" s="179"/>
-      <c r="N14" s="160">
+        <v>102901.79</v>
+      </c>
+      <c r="M14" s="177"/>
+      <c r="N14" s="159">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>189415.02</v>
-      </c>
-      <c r="O14" s="158">
+        <v>260717.02</v>
+      </c>
+      <c r="O14" s="157">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>200780.02</v>
-      </c>
-      <c r="P14" s="159">
+        <v>276360.02</v>
+      </c>
+      <c r="P14" s="158">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>195097.02</v>
+        <v>268539.02</v>
       </c>
       <c r="Q14" s="29">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>3</v>
       </c>
@@ -3276,11 +3264,11 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="54">
-        <v>188075.03</v>
+        <v>135021.03</v>
       </c>
       <c r="G15" s="55">
         <f>F15</f>
-        <v>188075.03</v>
+        <v>135021.03</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="0"/>
@@ -3298,29 +3286,29 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="161">
+      <c r="L15" s="160">
         <f>EDESUR!I7</f>
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="M15" s="177"/>
-      <c r="N15" s="160">
+        <v>3655.79</v>
+      </c>
+      <c r="M15" s="175"/>
+      <c r="N15" s="159">
         <f t="shared" si="4"/>
-        <v>135021.03</v>
+        <v>133256.03</v>
       </c>
       <c r="O15" s="57">
         <f t="shared" si="5"/>
-        <v>143122.03</v>
+        <v>141251.03</v>
       </c>
       <c r="P15" s="58">
         <f t="shared" si="6"/>
-        <v>139072.03</v>
+        <v>137254.03</v>
       </c>
       <c r="Q15" s="29">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44">
         <v>4</v>
       </c>
@@ -3337,19 +3325,19 @@
         <v>6.6</v>
       </c>
       <c r="F16" s="54">
-        <v>145200.04</v>
+        <v>158400.04</v>
       </c>
       <c r="G16" s="55">
-        <f>158400.2-G32</f>
-        <v>145200</v>
+        <f>178400.24-G32</f>
+        <v>164000.03999999998</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="0"/>
-        <v>4.0000000008149073E-2</v>
+        <v>-5599.9999999999709</v>
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
-        <v>1.2000000002444721E-3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="106">
         <f t="shared" si="1"/>
@@ -3359,83 +3347,83 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="161">
+      <c r="L16" s="160">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="178"/>
-      <c r="N16" s="160">
+      <c r="M16" s="176"/>
+      <c r="N16" s="159">
         <f t="shared" si="4"/>
-        <v>158400.04</v>
+        <v>152800.04</v>
       </c>
       <c r="O16" s="57">
         <f t="shared" si="5"/>
-        <v>167904.04</v>
+        <v>161968.04</v>
       </c>
       <c r="P16" s="58">
         <f t="shared" si="6"/>
-        <v>163152.04</v>
+        <v>157384.04</v>
       </c>
       <c r="Q16" s="29">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="153">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="152">
         <v>5</v>
       </c>
-      <c r="B17" s="153" t="s">
+      <c r="B17" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="153" t="s">
+      <c r="C17" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="153" t="s">
+      <c r="D17" s="152" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="155">
+      <c r="E17" s="154">
         <v>6.6</v>
       </c>
       <c r="F17" s="55">
-        <v>145200.04999999999</v>
+        <v>158400.04999999999</v>
       </c>
       <c r="G17" s="55">
         <f>F17</f>
-        <v>145200.04999999999</v>
-      </c>
-      <c r="H17" s="156">
+        <v>158400.04999999999</v>
+      </c>
+      <c r="H17" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="156">
+      <c r="I17" s="155">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="157">
+      <c r="J17" s="156">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K17" s="157">
+      <c r="K17" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="164">
+      <c r="L17" s="163">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="179">
-        <v>0</v>
-      </c>
-      <c r="N17" s="160">
+      <c r="M17" s="177">
+        <v>0</v>
+      </c>
+      <c r="N17" s="159">
         <f t="shared" si="4"/>
         <v>158400.04999999999</v>
       </c>
-      <c r="O17" s="158">
+      <c r="O17" s="157">
         <f t="shared" si="5"/>
         <v>167904.05</v>
       </c>
-      <c r="P17" s="159">
+      <c r="P17" s="158">
         <f t="shared" si="6"/>
         <v>163152.04999999999</v>
       </c>
@@ -3447,7 +3435,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44">
         <v>6</v>
       </c>
@@ -3464,19 +3452,18 @@
         <v>5.4</v>
       </c>
       <c r="F18" s="54">
-        <v>118800.06</v>
+        <v>129600.06</v>
       </c>
       <c r="G18" s="55">
-        <f t="shared" ref="G18" si="8">F18</f>
-        <v>118800.06</v>
+        <v>118800</v>
       </c>
       <c r="H18" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10800.059999999998</v>
       </c>
       <c r="I18" s="56">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>324.00179999999995</v>
       </c>
       <c r="J18" s="106">
         <f t="shared" si="1"/>
@@ -3486,151 +3473,148 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="161">
+      <c r="L18" s="160">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="178"/>
-      <c r="N18" s="160">
+      <c r="M18" s="176"/>
+      <c r="N18" s="159">
         <f t="shared" si="4"/>
-        <v>129600.06</v>
+        <v>140724.06</v>
       </c>
       <c r="O18" s="57">
         <f t="shared" si="5"/>
-        <v>137376.06</v>
+        <v>149168.06</v>
       </c>
       <c r="P18" s="58">
         <f t="shared" si="6"/>
-        <v>133488.06</v>
+        <v>144946.06</v>
       </c>
       <c r="Q18" s="29">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="153">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="152">
         <v>7</v>
       </c>
-      <c r="B19" s="153" t="s">
+      <c r="B19" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="153" t="s">
+      <c r="C19" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="153" t="s">
+      <c r="D19" s="152" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="155">
+      <c r="E19" s="154">
         <v>5.4</v>
       </c>
       <c r="F19" s="55">
-        <v>122364.07</v>
-      </c>
-      <c r="G19" s="55">
-        <f>F19</f>
-        <v>122364.07</v>
-      </c>
-      <c r="H19" s="156">
+        <v>129600.07</v>
+      </c>
+      <c r="G19" s="55"/>
+      <c r="H19" s="155">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="156">
+        <v>129600.07</v>
+      </c>
+      <c r="I19" s="155">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="157">
+        <v>3888.0021000000002</v>
+      </c>
+      <c r="J19" s="156">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K19" s="157">
+      <c r="K19" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="161">
+      <c r="L19" s="160">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="178"/>
-      <c r="N19" s="160">
+      <c r="M19" s="176"/>
+      <c r="N19" s="159">
         <f t="shared" si="4"/>
-        <v>129600.07</v>
-      </c>
-      <c r="O19" s="158">
+        <v>263088.07</v>
+      </c>
+      <c r="O19" s="157">
         <f t="shared" si="5"/>
-        <v>137376.07</v>
-      </c>
-      <c r="P19" s="159">
+        <v>278873.07</v>
+      </c>
+      <c r="P19" s="158">
         <f t="shared" si="6"/>
-        <v>133488.07</v>
+        <v>270981.07</v>
       </c>
       <c r="Q19" s="29">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="153">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="152">
         <v>8</v>
       </c>
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="153" t="s">
+      <c r="C20" s="152" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="154" t="s">
+      <c r="D20" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="155">
+      <c r="E20" s="154">
         <v>6.6</v>
       </c>
       <c r="F20" s="55">
-        <v>222130.08</v>
+        <v>225080.08</v>
       </c>
       <c r="G20" s="55">
         <f>F20</f>
-        <v>222130.08</v>
-      </c>
-      <c r="H20" s="156">
+        <v>225080.08</v>
+      </c>
+      <c r="H20" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="156">
+      <c r="I20" s="155">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="157">
+      <c r="J20" s="156">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K20" s="157">
+      <c r="K20" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="161">
+      <c r="L20" s="160">
         <f>EDESUR!I13</f>
-        <v>66680.352219450724</v>
-      </c>
-      <c r="M20" s="178"/>
-      <c r="N20" s="160">
+        <v>63231.57</v>
+      </c>
+      <c r="M20" s="176"/>
+      <c r="N20" s="159">
         <f t="shared" si="4"/>
-        <v>225080.08</v>
-      </c>
-      <c r="O20" s="158">
+        <v>221632.08</v>
+      </c>
+      <c r="O20" s="157">
         <f t="shared" si="5"/>
-        <v>238585.08</v>
-      </c>
-      <c r="P20" s="159">
+        <v>234930.08</v>
+      </c>
+      <c r="P20" s="158">
         <f t="shared" si="6"/>
-        <v>231832.08</v>
+        <v>228281.08</v>
       </c>
       <c r="Q20" s="29">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44">
         <v>9</v>
       </c>
@@ -3647,11 +3631,11 @@
         <v>6.6</v>
       </c>
       <c r="F21" s="54">
-        <v>106012.09</v>
+        <v>130013.09</v>
       </c>
       <c r="G21" s="55">
         <f>F21+28387</f>
-        <v>134399.09</v>
+        <v>158400.09</v>
       </c>
       <c r="H21" s="56">
         <f t="shared" si="0"/>
@@ -3669,12 +3653,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="161">
+      <c r="L21" s="160">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="178"/>
-      <c r="N21" s="160">
+      <c r="M21" s="176"/>
+      <c r="N21" s="159">
         <f t="shared" si="4"/>
         <v>130013.09</v>
       </c>
@@ -3691,7 +3675,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="44">
         <v>10</v>
       </c>
@@ -3708,15 +3692,15 @@
         <v>5.4</v>
       </c>
       <c r="F22" s="54">
-        <v>9.9999999999999992E-2</v>
+        <v>-0.9</v>
       </c>
       <c r="G22" s="55">
-        <f>RESUMEN!D41-28387</f>
+        <f>RESUMEN!D39-28387</f>
         <v>129601.29000000001</v>
       </c>
       <c r="H22" s="56">
         <f>F22-G22</f>
-        <v>-129601.19</v>
+        <v>-129602.19</v>
       </c>
       <c r="I22" s="56">
         <f t="shared" si="3"/>
@@ -3730,29 +3714,29 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="161">
+      <c r="L22" s="160">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="178"/>
-      <c r="N22" s="160">
+      <c r="M22" s="176"/>
+      <c r="N22" s="159">
         <f t="shared" si="4"/>
-        <v>-0.9</v>
+        <v>-1.9</v>
       </c>
       <c r="O22" s="57">
         <f t="shared" si="5"/>
-        <v>-0.9</v>
+        <v>-1.9</v>
       </c>
       <c r="P22" s="58">
         <f t="shared" si="6"/>
-        <v>-0.9</v>
+        <v>-1.9</v>
       </c>
       <c r="Q22" s="29">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44">
         <v>11</v>
       </c>
@@ -3767,11 +3751,11 @@
         <v>5.4</v>
       </c>
       <c r="F23" s="54">
-        <v>118800.11</v>
+        <v>129600.11</v>
       </c>
       <c r="G23" s="55">
-        <f>125400-G34</f>
-        <v>118799.78</v>
+        <f>136800-G34</f>
+        <v>129599.78</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="0"/>
@@ -3789,12 +3773,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="161">
+      <c r="L23" s="160">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="178"/>
-      <c r="N23" s="160">
+      <c r="M23" s="176"/>
+      <c r="N23" s="159">
         <f t="shared" si="4"/>
         <v>129600.11</v>
       </c>
@@ -3814,7 +3798,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="44">
         <v>12</v>
       </c>
@@ -3831,11 +3815,11 @@
         <v>6.6</v>
       </c>
       <c r="F24" s="54">
-        <v>145200.12</v>
+        <v>158400.12</v>
       </c>
       <c r="G24" s="55">
         <f>F24</f>
-        <v>145200.12</v>
+        <v>158400.12</v>
       </c>
       <c r="H24" s="56">
         <f t="shared" si="0"/>
@@ -3853,12 +3837,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="161">
+      <c r="L24" s="160">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="178"/>
-      <c r="N24" s="160">
+      <c r="M24" s="176"/>
+      <c r="N24" s="159">
         <f t="shared" si="4"/>
         <v>158400.12</v>
       </c>
@@ -3875,7 +3859,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44">
         <v>13</v>
       </c>
@@ -3892,14 +3876,14 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="54">
-        <v>145200.13</v>
+        <v>154044.13</v>
       </c>
       <c r="G25" s="55">
-        <v>149556.13</v>
+        <v>158665.13</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="0"/>
-        <v>-4356</v>
+        <v>-4621</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
@@ -3913,79 +3897,79 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="161">
+      <c r="L25" s="160">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="178"/>
-      <c r="N25" s="160">
+      <c r="M25" s="176"/>
+      <c r="N25" s="159">
         <f t="shared" si="4"/>
-        <v>154044.13</v>
+        <v>153779.13</v>
       </c>
       <c r="O25" s="57">
         <f t="shared" si="5"/>
-        <v>163287.13</v>
+        <v>163006.13</v>
       </c>
       <c r="P25" s="58">
         <f t="shared" si="6"/>
-        <v>158665.13</v>
+        <v>158392.13</v>
       </c>
       <c r="Q25" s="29">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="153">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="152">
         <v>14</v>
       </c>
-      <c r="B26" s="153" t="s">
+      <c r="B26" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="154"/>
-      <c r="E26" s="155">
+      <c r="D26" s="153"/>
+      <c r="E26" s="154">
         <v>5.4</v>
       </c>
       <c r="F26" s="55">
-        <v>118800.14</v>
+        <v>129600.14</v>
       </c>
       <c r="G26" s="55">
         <f>F26</f>
-        <v>118800.14</v>
-      </c>
-      <c r="H26" s="156">
+        <v>129600.14</v>
+      </c>
+      <c r="H26" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="156">
+      <c r="I26" s="155">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="157">
+      <c r="J26" s="156">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K26" s="157">
+      <c r="K26" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="164">
+      <c r="L26" s="163">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="179"/>
-      <c r="N26" s="160">
+      <c r="M26" s="177"/>
+      <c r="N26" s="159">
         <f t="shared" si="4"/>
         <v>129600.14</v>
       </c>
-      <c r="O26" s="158">
+      <c r="O26" s="157">
         <f t="shared" si="5"/>
         <v>137376.14000000001</v>
       </c>
-      <c r="P26" s="159">
+      <c r="P26" s="158">
         <f t="shared" si="6"/>
         <v>133488.14000000001</v>
       </c>
@@ -3994,7 +3978,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44">
         <v>15</v>
       </c>
@@ -4009,11 +3993,11 @@
         <v>5.4</v>
       </c>
       <c r="F27" s="54">
-        <v>241164.15</v>
+        <v>129600.15</v>
       </c>
       <c r="G27" s="55">
         <f>F27</f>
-        <v>241164.15</v>
+        <v>129600.15</v>
       </c>
       <c r="H27" s="56">
         <f t="shared" si="0"/>
@@ -4031,12 +4015,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="161">
+      <c r="L27" s="160">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="178"/>
-      <c r="N27" s="160">
+      <c r="M27" s="176"/>
+      <c r="N27" s="159">
         <f t="shared" si="4"/>
         <v>129600.15</v>
       </c>
@@ -4053,14 +4037,14 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="152">
         <v>16</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="152" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="152" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="44" t="s">
@@ -4070,19 +4054,18 @@
         <v>0.7</v>
       </c>
       <c r="F28" s="54">
-        <v>15400.16</v>
+        <v>16800.16</v>
       </c>
       <c r="G28" s="55">
-        <f t="shared" ref="G28:G34" si="9">F28</f>
-        <v>15400.16</v>
+        <v>15400</v>
       </c>
       <c r="H28" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1400.1599999999999</v>
       </c>
       <c r="I28" s="56">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>42.004799999999996</v>
       </c>
       <c r="J28" s="106">
         <f t="shared" si="1"/>
@@ -4092,36 +4075,36 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="161">
+      <c r="L28" s="160">
         <f>EDESUR!I22</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="178"/>
-      <c r="N28" s="160">
+        <v>266.88</v>
+      </c>
+      <c r="M28" s="176"/>
+      <c r="N28" s="159">
         <f t="shared" si="4"/>
-        <v>16800.16</v>
+        <v>18509.16</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" si="5"/>
-        <v>17808.16</v>
+        <v>19620.16</v>
       </c>
       <c r="P28" s="58">
         <f t="shared" si="6"/>
-        <v>17304.16</v>
+        <v>19064.16</v>
       </c>
       <c r="Q28" s="29">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="234">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="152">
         <v>17</v>
       </c>
-      <c r="B29" s="234" t="s">
+      <c r="B29" s="152" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="234" t="s">
+      <c r="C29" s="152" t="s">
         <v>28</v>
       </c>
       <c r="D29" s="45"/>
@@ -4129,14 +4112,15 @@
         <v>0.6</v>
       </c>
       <c r="F29" s="55">
-        <v>13200.17</v>
+        <v>1200.17</v>
       </c>
       <c r="G29" s="55">
-        <v>26400.17</v>
+        <f>F29</f>
+        <v>1200.17</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="0"/>
-        <v>-13199.999999999998</v>
+        <v>0</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
@@ -4150,29 +4134,29 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="161">
+      <c r="L29" s="160">
         <f>EDESUR!I23</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="178"/>
-      <c r="N29" s="160">
+        <v>228.75</v>
+      </c>
+      <c r="M29" s="176"/>
+      <c r="N29" s="159">
         <f t="shared" si="4"/>
-        <v>1200.17</v>
+        <v>14629.17</v>
       </c>
       <c r="O29" s="57">
         <f t="shared" si="5"/>
-        <v>1272.17</v>
+        <v>15507.17</v>
       </c>
       <c r="P29" s="58">
         <f t="shared" si="6"/>
-        <v>1236.17</v>
+        <v>15068.17</v>
       </c>
       <c r="Q29" s="29">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="44">
         <v>18</v>
       </c>
@@ -4187,18 +4171,19 @@
         <v>0.6</v>
       </c>
       <c r="F30" s="54">
-        <v>13200.18</v>
+        <v>27996.18</v>
       </c>
       <c r="G30" s="55">
-        <v>0</v>
+        <f>F30</f>
+        <v>27996.18</v>
       </c>
       <c r="H30" s="56">
         <f t="shared" si="0"/>
-        <v>13200.18</v>
+        <v>0</v>
       </c>
       <c r="I30" s="56">
         <f t="shared" si="3"/>
-        <v>396.00540000000001</v>
+        <v>0</v>
       </c>
       <c r="J30" s="106">
         <f t="shared" si="1"/>
@@ -4208,85 +4193,85 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="161">
+      <c r="L30" s="160">
         <f>EDESUR!I24</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="178"/>
-      <c r="N30" s="160">
+        <v>228.75</v>
+      </c>
+      <c r="M30" s="176"/>
+      <c r="N30" s="159">
         <f t="shared" si="4"/>
-        <v>27996.18</v>
+        <v>14629.18</v>
       </c>
       <c r="O30" s="57">
         <f t="shared" si="5"/>
-        <v>29676.18</v>
+        <v>15507.18</v>
       </c>
       <c r="P30" s="58">
         <f t="shared" si="6"/>
-        <v>28836.18</v>
+        <v>15068.18</v>
       </c>
       <c r="Q30" s="29">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="153">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="152">
         <v>19</v>
       </c>
-      <c r="B31" s="153" t="s">
+      <c r="B31" s="152" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="153" t="s">
+      <c r="C31" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="155">
+      <c r="D31" s="153"/>
+      <c r="E31" s="154">
         <v>0.6</v>
       </c>
       <c r="F31" s="55">
-        <v>13200.19</v>
+        <v>14400.19</v>
       </c>
       <c r="G31" s="55">
         <f>F31</f>
-        <v>13200.19</v>
-      </c>
-      <c r="H31" s="156">
+        <v>14400.19</v>
+      </c>
+      <c r="H31" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="156">
+      <c r="I31" s="155">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="157">
+      <c r="J31" s="156">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
-      <c r="K31" s="157">
+      <c r="K31" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="164">
+      <c r="L31" s="163">
         <f>EDESUR!I25</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="179"/>
-      <c r="N31" s="160">
+        <v>228.75</v>
+      </c>
+      <c r="M31" s="177"/>
+      <c r="N31" s="159">
         <f t="shared" si="4"/>
-        <v>14400.19</v>
-      </c>
-      <c r="O31" s="158"/>
-      <c r="P31" s="159">
+        <v>14629.19</v>
+      </c>
+      <c r="O31" s="157"/>
+      <c r="P31" s="158">
         <f t="shared" si="6"/>
-        <v>14832.19</v>
+        <v>15068.19</v>
       </c>
       <c r="Q31" s="29">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="59">
         <v>20</v>
       </c>
@@ -4303,11 +4288,11 @@
         <v>0.6</v>
       </c>
       <c r="F32" s="61">
-        <v>13200.2</v>
+        <v>14400.2</v>
       </c>
       <c r="G32" s="55">
         <f>F32</f>
-        <v>13200.2</v>
+        <v>14400.2</v>
       </c>
       <c r="H32" s="56">
         <f t="shared" si="0"/>
@@ -4325,26 +4310,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="161">
+      <c r="L32" s="160">
         <f>EDESUR!I26</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="178"/>
-      <c r="N32" s="160">
+        <v>228.75</v>
+      </c>
+      <c r="M32" s="176"/>
+      <c r="N32" s="159">
         <f t="shared" si="4"/>
-        <v>14400.2</v>
+        <v>14629.2</v>
       </c>
       <c r="O32" s="57"/>
       <c r="P32" s="58">
         <f t="shared" si="6"/>
-        <v>14832.2</v>
+        <v>15068.2</v>
       </c>
       <c r="Q32" s="29">
-        <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
+        <f t="shared" ref="Q32:Q35" si="8">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="59">
         <v>21</v>
       </c>
@@ -4361,14 +4346,15 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="61">
-        <v>6600.21</v>
+        <v>7002.21</v>
       </c>
       <c r="G33" s="55">
-        <v>6798.21</v>
+        <f>F33</f>
+        <v>7002.21</v>
       </c>
       <c r="H33" s="56">
         <f t="shared" si="0"/>
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="I33" s="56">
         <f t="shared" si="3"/>
@@ -4382,26 +4368,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="161">
+      <c r="L33" s="160">
         <f>EDESUR!I27</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="178"/>
-      <c r="N33" s="160">
+        <v>114.38</v>
+      </c>
+      <c r="M33" s="176"/>
+      <c r="N33" s="159">
         <f t="shared" si="4"/>
-        <v>7002.21</v>
+        <v>7314.21</v>
       </c>
       <c r="O33" s="57"/>
       <c r="P33" s="58">
         <f t="shared" si="6"/>
-        <v>7212.21</v>
+        <v>7533.21</v>
       </c>
       <c r="Q33" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>22</v>
       </c>
@@ -4416,11 +4402,11 @@
         <v>0.3</v>
       </c>
       <c r="F34" s="61">
-        <v>6600.22</v>
-      </c>
-      <c r="G34" s="152">
-        <f t="shared" si="9"/>
-        <v>6600.22</v>
+        <v>7200.22</v>
+      </c>
+      <c r="G34" s="151">
+        <f t="shared" ref="G28:G34" si="9">F34</f>
+        <v>7200.22</v>
       </c>
       <c r="H34" s="56">
         <f t="shared" si="0"/>
@@ -4438,26 +4424,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="161">
+      <c r="L34" s="160">
         <f>EDESUR!I28</f>
-        <v>0</v>
-      </c>
-      <c r="M34" s="178"/>
-      <c r="N34" s="160">
+        <v>114.38</v>
+      </c>
+      <c r="M34" s="176"/>
+      <c r="N34" s="159">
         <f t="shared" si="4"/>
-        <v>7200.22</v>
+        <v>7314.22</v>
       </c>
       <c r="O34" s="57"/>
       <c r="P34" s="58">
         <f t="shared" si="6"/>
-        <v>7416.22</v>
+        <v>7533.22</v>
       </c>
       <c r="Q34" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="44">
         <v>23</v>
       </c>
@@ -4474,11 +4460,11 @@
         <v>0.3</v>
       </c>
       <c r="F35" s="61">
-        <v>6600.23</v>
+        <v>7200.23</v>
       </c>
       <c r="G35" s="55">
         <f>F35</f>
-        <v>6600.23</v>
+        <v>7200.23</v>
       </c>
       <c r="H35" s="56">
         <f t="shared" si="0"/>
@@ -4496,26 +4482,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="161">
+      <c r="L35" s="160">
         <f>EDESUR!I29</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="178"/>
-      <c r="N35" s="160">
+        <v>114.38</v>
+      </c>
+      <c r="M35" s="176"/>
+      <c r="N35" s="159">
         <f t="shared" si="4"/>
-        <v>7200.23</v>
+        <v>7314.23</v>
       </c>
       <c r="O35" s="63"/>
       <c r="P35" s="58">
         <f t="shared" si="6"/>
-        <v>7416.23</v>
+        <v>7533.23</v>
       </c>
       <c r="Q35" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="64"/>
       <c r="B36" s="64"/>
       <c r="C36" s="65"/>
@@ -4526,140 +4512,146 @@
       </c>
       <c r="F36" s="38">
         <f>SUM(F13:F35)</f>
-        <v>2348836.7600000012</v>
+        <v>2340972.7600000012</v>
       </c>
       <c r="G36" s="42">
         <f>SUM(G13:G35)</f>
-        <v>2511489.3800000008</v>
+        <v>2367966.9600000004</v>
       </c>
       <c r="H36" s="42">
         <f>SUM(H13:H35)</f>
-        <v>-162652.62</v>
+        <v>-26994.2</v>
       </c>
       <c r="I36" s="42">
-        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
-        <v>396.01650000000029</v>
+        <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
+        <v>4254.0290999999988</v>
       </c>
       <c r="J36" s="92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2400000</v>
       </c>
       <c r="K36" s="42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L36" s="66">
         <f>SUM(L13:L35)</f>
-        <v>103227.02696710824</v>
+        <v>171314.17</v>
       </c>
       <c r="M36" s="66"/>
       <c r="N36" s="66">
         <f>SUM(N13:N35)</f>
-        <v>2340972.7600000012</v>
+        <v>2548576.7600000012</v>
       </c>
       <c r="O36" s="66">
-        <f t="shared" si="11"/>
-        <v>2428216.7100000009</v>
+        <f t="shared" si="10"/>
+        <v>2647219.7100000009</v>
       </c>
       <c r="P36" s="66">
         <f>SUM(P13:P35)</f>
-        <v>2411200.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2625033.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="193" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="196" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="193"/>
-      <c r="E39" s="193"/>
-      <c r="F39" s="193"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
-      <c r="I39" s="193"/>
-      <c r="J39" s="193"/>
-      <c r="K39" s="193"/>
-      <c r="L39" s="193"/>
-      <c r="M39" s="193"/>
-      <c r="N39" s="193"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="193"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="193"/>
-      <c r="K40" s="193"/>
-      <c r="L40" s="193"/>
-      <c r="M40" s="193"/>
-      <c r="N40" s="193"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="193"/>
-      <c r="D41" s="193"/>
-      <c r="E41" s="193"/>
-      <c r="F41" s="193"/>
-      <c r="G41" s="193"/>
-      <c r="H41" s="193"/>
-      <c r="I41" s="193"/>
-      <c r="J41" s="193"/>
-      <c r="K41" s="193"/>
-      <c r="L41" s="193"/>
-      <c r="M41" s="193"/>
-      <c r="N41" s="193"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="193"/>
-      <c r="D42" s="193"/>
-      <c r="E42" s="193"/>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="193"/>
-      <c r="I42" s="193"/>
-      <c r="J42" s="193"/>
-      <c r="K42" s="193"/>
-      <c r="L42" s="193"/>
-      <c r="M42" s="193"/>
-      <c r="N42" s="193"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="193"/>
-      <c r="D43" s="193"/>
-      <c r="E43" s="193"/>
-      <c r="F43" s="193"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="193"/>
-      <c r="I43" s="193"/>
-      <c r="J43" s="193"/>
-      <c r="K43" s="193"/>
-      <c r="L43" s="193"/>
-      <c r="M43" s="193"/>
-      <c r="N43" s="193"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="193"/>
-      <c r="D44" s="193"/>
-      <c r="E44" s="193"/>
-      <c r="F44" s="193"/>
-      <c r="G44" s="193"/>
-      <c r="H44" s="193"/>
-      <c r="I44" s="193"/>
-      <c r="J44" s="193"/>
-      <c r="K44" s="193"/>
-      <c r="L44" s="193"/>
-      <c r="M44" s="193"/>
-      <c r="N44" s="193"/>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="196"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="196"/>
+      <c r="I39" s="196"/>
+      <c r="J39" s="196"/>
+      <c r="K39" s="196"/>
+      <c r="L39" s="196"/>
+      <c r="M39" s="196"/>
+      <c r="N39" s="196"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="196"/>
+      <c r="D40" s="196"/>
+      <c r="E40" s="196"/>
+      <c r="F40" s="196"/>
+      <c r="G40" s="196"/>
+      <c r="H40" s="196"/>
+      <c r="I40" s="196"/>
+      <c r="J40" s="196"/>
+      <c r="K40" s="196"/>
+      <c r="L40" s="196"/>
+      <c r="M40" s="196"/>
+      <c r="N40" s="196"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="196"/>
+      <c r="D41" s="196"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="196"/>
+      <c r="G41" s="196"/>
+      <c r="H41" s="196"/>
+      <c r="I41" s="196"/>
+      <c r="J41" s="196"/>
+      <c r="K41" s="196"/>
+      <c r="L41" s="196"/>
+      <c r="M41" s="196"/>
+      <c r="N41" s="196"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="196"/>
+      <c r="D42" s="196"/>
+      <c r="E42" s="196"/>
+      <c r="F42" s="196"/>
+      <c r="G42" s="196"/>
+      <c r="H42" s="196"/>
+      <c r="I42" s="196"/>
+      <c r="J42" s="196"/>
+      <c r="K42" s="196"/>
+      <c r="L42" s="196"/>
+      <c r="M42" s="196"/>
+      <c r="N42" s="196"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="196"/>
+      <c r="D43" s="196"/>
+      <c r="E43" s="196"/>
+      <c r="F43" s="196"/>
+      <c r="G43" s="196"/>
+      <c r="H43" s="196"/>
+      <c r="I43" s="196"/>
+      <c r="J43" s="196"/>
+      <c r="K43" s="196"/>
+      <c r="L43" s="196"/>
+      <c r="M43" s="196"/>
+      <c r="N43" s="196"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="196"/>
+      <c r="D44" s="196"/>
+      <c r="E44" s="196"/>
+      <c r="F44" s="196"/>
+      <c r="G44" s="196"/>
+      <c r="H44" s="196"/>
+      <c r="I44" s="196"/>
+      <c r="J44" s="196"/>
+      <c r="K44" s="196"/>
+      <c r="L44" s="196"/>
+      <c r="M44" s="196"/>
+      <c r="N44" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4673,12 +4665,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4686,601 +4672,616 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
-  <dimension ref="C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C2" s="235" t="s">
-        <v>150</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="120" t="s">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="E3" s="121" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="150" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="232" t="s">
+      <c r="I3" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="233"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="G4" s="123"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="233"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="120">
+      <c r="J3" s="228"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="G4" s="122"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="228"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="119">
         <v>1</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C5" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="180">
-        <v>12046.778334087237</v>
+      <c r="E5" s="178">
+        <v>8123.99</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="181">
-        <v>12046.778334087237</v>
-      </c>
-      <c r="I5" s="230">
+      <c r="G5" s="179">
+        <f>E5</f>
+        <v>8123.99</v>
+      </c>
+      <c r="I5" s="225">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="231"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="120">
+      <c r="J5" s="226"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="119">
         <v>1</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C6" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="180">
-        <v>31125.624497318255</v>
+      <c r="E6" s="178">
+        <v>102901.79</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="181">
-        <v>0</v>
-      </c>
-      <c r="I6" s="230">
+      <c r="G6" s="179">
+        <v>0</v>
+      </c>
+      <c r="I6" s="225">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
-        <v>31125.624497318255</v>
-      </c>
-      <c r="J6" s="231"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="120">
+        <v>102901.79</v>
+      </c>
+      <c r="J6" s="226"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="119">
         <v>1</v>
       </c>
-      <c r="C7" s="120" t="s">
+      <c r="C7" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E7" s="178">
+        <v>3655.79</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="181">
-        <v>0</v>
-      </c>
-      <c r="I7" s="230">
+      <c r="G7" s="179">
+        <v>0</v>
+      </c>
+      <c r="I7" s="225">
         <f t="shared" si="0"/>
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="J7" s="231"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="120">
+        <v>3655.79</v>
+      </c>
+      <c r="J7" s="226"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="119">
         <v>2</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="C8" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E8" s="178">
+        <v>3655.79</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I8" s="230">
+      <c r="G8" s="179">
+        <f>E8</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I8" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="231"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="121">
+      <c r="J8" s="226"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="120">
         <v>2</v>
       </c>
-      <c r="C9" s="121" t="s">
+      <c r="C9" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="180">
-        <v>6625.7280837479811</v>
+      <c r="E9" s="178">
+        <v>4468.1899999999996</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="181">
-        <v>6625.7280837479811</v>
-      </c>
-      <c r="I9" s="230">
+      <c r="G9" s="179">
+        <f>E9</f>
+        <v>4468.1899999999996</v>
+      </c>
+      <c r="I9" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="231"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="121">
+      <c r="J9" s="226"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="120">
         <v>2</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="180">
-        <v>6625.7280837479811</v>
+      <c r="E10" s="178">
+        <v>4468.1899999999996</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="181">
-        <v>6625.7280837479811</v>
-      </c>
-      <c r="I10" s="230">
+      <c r="G10" s="179">
+        <f>E10</f>
+        <v>4468.1899999999996</v>
+      </c>
+      <c r="I10" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="231"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="121">
+      <c r="J10" s="226"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="120">
         <v>2</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E11" s="178">
+        <v>3655.79</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I11" s="230">
+      <c r="G11" s="179">
+        <f>E11</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I11" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="231"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="121">
+      <c r="J11" s="226"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="120">
         <v>3</v>
       </c>
-      <c r="C12" s="121" t="s">
+      <c r="C12" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E12" s="178">
+        <v>3655.79</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I12" s="230">
+      <c r="G12" s="179">
+        <f>E12</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I12" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="231"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="120">
+      <c r="J12" s="226"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="119">
         <v>3</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="180">
-        <v>66680.352219450724</v>
+      <c r="E13" s="178">
+        <v>63231.57</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="181">
-        <v>0</v>
-      </c>
-      <c r="I13" s="230">
+      <c r="G13" s="179">
+        <v>0</v>
+      </c>
+      <c r="I13" s="225">
         <f t="shared" si="0"/>
-        <v>66680.352219450724</v>
-      </c>
-      <c r="J13" s="231"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="121">
+        <v>63231.57</v>
+      </c>
+      <c r="J13" s="226"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="120">
         <v>3</v>
       </c>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="180">
-        <v>6625.7280837479811</v>
+      <c r="E14" s="178">
+        <f>E10</f>
+        <v>4468.1899999999996</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="181">
-        <v>6625.7280837479811</v>
-      </c>
-      <c r="I14" s="230">
+      <c r="G14" s="179">
+        <f>E14</f>
+        <v>4468.1899999999996</v>
+      </c>
+      <c r="I14" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="231"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="121">
+      <c r="J14" s="226"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="120">
         <v>3</v>
       </c>
-      <c r="C15" s="121" t="s">
+      <c r="C15" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E15" s="178">
+        <f>E12</f>
+        <v>3655.79</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I15" s="230">
+      <c r="G15" s="179">
+        <f>E15</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I15" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="231"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="120">
+      <c r="J15" s="226"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="119">
         <v>4</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E16" s="178">
+        <f>E15</f>
+        <v>3655.79</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I16" s="230">
+      <c r="G16" s="179">
+        <f>E16</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I16" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="231"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="121">
+      <c r="J16" s="226"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="120">
         <v>4</v>
       </c>
-      <c r="C17" s="121" t="s">
+      <c r="C17" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="180">
-        <v>6625.7280837479811</v>
+      <c r="E17" s="178">
+        <f>E14</f>
+        <v>4468.1899999999996</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="181">
-        <v>6625.7280837479811</v>
-      </c>
-      <c r="I17" s="230">
+      <c r="G17" s="179">
+        <f>E17</f>
+        <v>4468.1899999999996</v>
+      </c>
+      <c r="I17" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="231"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="120">
+      <c r="J17" s="226"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="119">
         <v>4</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="180">
-        <v>6625.7280837479811</v>
+      <c r="E18" s="178">
+        <f>E17</f>
+        <v>4468.1899999999996</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="181">
-        <v>6625.7280837479811</v>
-      </c>
-      <c r="I18" s="230">
+      <c r="G18" s="179">
+        <f>E18</f>
+        <v>4468.1899999999996</v>
+      </c>
+      <c r="I18" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="231"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="121">
+      <c r="J18" s="226"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="120">
         <v>4</v>
       </c>
-      <c r="C19" s="121" t="s">
+      <c r="C19" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="180">
-        <v>5421.0502503392572</v>
+      <c r="E19" s="178">
+        <f>E16</f>
+        <v>3655.79</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="181">
-        <v>5421.0502503392572</v>
-      </c>
-      <c r="I19" s="230">
+      <c r="G19" s="179">
+        <f>E19</f>
+        <v>3655.79</v>
+      </c>
+      <c r="I19" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="231"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="G20" s="123"/>
-      <c r="I20" s="230"/>
-      <c r="J20" s="231"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="144" t="s">
+      <c r="J19" s="226"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="G20" s="122"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="226"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="143" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="144"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="146">
+      <c r="C21" s="143"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="145">
         <f>SUM(E5:E20)</f>
-        <v>180928.74722197096</v>
-      </c>
-      <c r="F21" s="147"/>
-      <c r="G21" s="146">
+        <v>222188.83000000002</v>
+      </c>
+      <c r="F21" s="146"/>
+      <c r="G21" s="145">
         <f>SUM(G5:G20)</f>
-        <v>77701.720254862681</v>
-      </c>
-      <c r="I21" s="230">
+        <v>52399.68</v>
+      </c>
+      <c r="I21" s="225">
         <f>E21-G21</f>
-        <v>103227.02696710828</v>
-      </c>
-      <c r="J21" s="231"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="120" t="s">
+        <v>169789.15000000002</v>
+      </c>
+      <c r="J21" s="226"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="120">
+      <c r="C22" s="119">
         <v>1</v>
       </c>
-      <c r="E22" s="182">
-        <v>702.72873615508888</v>
-      </c>
-      <c r="G22" s="128">
-        <f>E22</f>
-        <v>702.72873615508888</v>
-      </c>
-      <c r="I22" s="230">
+      <c r="E22" s="180">
+        <v>473.9</v>
+      </c>
+      <c r="G22" s="127">
+        <v>207.02</v>
+      </c>
+      <c r="I22" s="225">
         <f t="shared" ref="I22" si="1">E22-G22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="231"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="120" t="s">
+        <v>266.88</v>
+      </c>
+      <c r="J22" s="226"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="120">
+      <c r="C23" s="119">
         <v>2</v>
       </c>
-      <c r="E23" s="182">
-        <v>602.33891670436185</v>
-      </c>
-      <c r="G23" s="128">
-        <f t="shared" ref="G23:G29" si="2">E23</f>
-        <v>602.33891670436185</v>
-      </c>
-      <c r="I23" s="230">
-        <f t="shared" ref="I23:I31" si="3">E23-G23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="231"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="120" t="s">
+      <c r="E23" s="180">
+        <v>406.2</v>
+      </c>
+      <c r="G23" s="127">
+        <v>177.45</v>
+      </c>
+      <c r="I23" s="225">
+        <f t="shared" ref="I23:I31" si="2">E23-G23</f>
+        <v>228.75</v>
+      </c>
+      <c r="J23" s="226"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="120">
+      <c r="C24" s="119">
         <v>3</v>
       </c>
-      <c r="E24" s="182">
-        <v>602.33891670436185</v>
-      </c>
-      <c r="G24" s="128">
+      <c r="E24" s="180">
+        <f>E23</f>
+        <v>406.2</v>
+      </c>
+      <c r="G24" s="127">
+        <v>177.45</v>
+      </c>
+      <c r="I24" s="225">
         <f t="shared" si="2"/>
-        <v>602.33891670436185</v>
-      </c>
-      <c r="I24" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="231"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="120" t="s">
+        <v>228.75</v>
+      </c>
+      <c r="J24" s="226"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="120">
+      <c r="C25" s="119">
         <v>4</v>
       </c>
-      <c r="E25" s="182">
-        <v>602.33891670436185</v>
-      </c>
-      <c r="G25" s="128">
+      <c r="E25" s="180">
+        <f>E24</f>
+        <v>406.2</v>
+      </c>
+      <c r="G25" s="127">
+        <v>177.45</v>
+      </c>
+      <c r="I25" s="225">
         <f t="shared" si="2"/>
-        <v>602.33891670436185</v>
-      </c>
-      <c r="I25" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="231"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="120" t="s">
+        <v>228.75</v>
+      </c>
+      <c r="J25" s="226"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="120">
+      <c r="C26" s="119">
         <v>5</v>
       </c>
-      <c r="E26" s="182">
-        <v>602.33891670436185</v>
-      </c>
-      <c r="G26" s="128">
+      <c r="E26" s="180">
+        <f>E25</f>
+        <v>406.2</v>
+      </c>
+      <c r="G26" s="127">
+        <v>177.45</v>
+      </c>
+      <c r="I26" s="225">
         <f t="shared" si="2"/>
-        <v>602.33891670436185</v>
-      </c>
-      <c r="I26" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="231"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="120" t="s">
+        <v>228.75</v>
+      </c>
+      <c r="J26" s="226"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="120">
+      <c r="C27" s="119">
         <v>6</v>
       </c>
-      <c r="E27" s="182">
-        <v>301.16945835218092</v>
-      </c>
-      <c r="G27" s="128">
+      <c r="E27" s="180">
+        <v>203.1</v>
+      </c>
+      <c r="G27" s="127">
+        <v>88.72</v>
+      </c>
+      <c r="I27" s="225">
         <f t="shared" si="2"/>
-        <v>301.16945835218092</v>
-      </c>
-      <c r="I27" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="231"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="120" t="s">
+        <v>114.38</v>
+      </c>
+      <c r="J27" s="226"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="120">
+      <c r="C28" s="119">
         <v>7</v>
       </c>
-      <c r="E28" s="182">
-        <v>301.16945835218092</v>
-      </c>
-      <c r="G28" s="128">
+      <c r="E28" s="180">
+        <f>E27</f>
+        <v>203.1</v>
+      </c>
+      <c r="G28" s="127">
+        <v>88.72</v>
+      </c>
+      <c r="I28" s="225">
         <f t="shared" si="2"/>
-        <v>301.16945835218092</v>
-      </c>
-      <c r="I28" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="231"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="120" t="s">
+        <v>114.38</v>
+      </c>
+      <c r="J28" s="226"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="120">
+      <c r="C29" s="119">
         <v>8</v>
       </c>
-      <c r="E29" s="182">
-        <v>301.16945835218092</v>
-      </c>
-      <c r="G29" s="128">
+      <c r="E29" s="180">
+        <f>E28</f>
+        <v>203.1</v>
+      </c>
+      <c r="G29" s="127">
+        <v>88.72</v>
+      </c>
+      <c r="I29" s="225">
         <f t="shared" si="2"/>
-        <v>301.16945835218092</v>
-      </c>
-      <c r="I29" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="231"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="149" t="s">
+        <v>114.38</v>
+      </c>
+      <c r="J29" s="226"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="148" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="150"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="146">
+      <c r="C30" s="149"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="145">
         <f>SUM(E22:E29)</f>
-        <v>4015.592778029079</v>
-      </c>
-      <c r="F30" s="148"/>
-      <c r="G30" s="146">
+        <v>2707.9999999999995</v>
+      </c>
+      <c r="F30" s="147"/>
+      <c r="G30" s="145">
         <f>SUM(G22:G29)</f>
-        <v>4015.592778029079</v>
-      </c>
-      <c r="I30" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="231"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="127"/>
-      <c r="G31" s="124"/>
-      <c r="I31" s="230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="231"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="125"/>
-      <c r="G32" s="126"/>
-      <c r="I32" s="230"/>
-      <c r="J32" s="231"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="127">
+        <v>1182.9800000000002</v>
+      </c>
+      <c r="I30" s="225">
+        <f t="shared" si="2"/>
+        <v>1525.0199999999993</v>
+      </c>
+      <c r="J30" s="226"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="126"/>
+      <c r="G31" s="123"/>
+      <c r="I31" s="225">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="226"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="124"/>
+      <c r="G32" s="125"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="226"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="126">
         <f>E30+E21</f>
-        <v>184944.34000000003</v>
-      </c>
-      <c r="G33" s="124">
+        <v>224896.83000000002</v>
+      </c>
+      <c r="G33" s="123">
         <f>G21+G30</f>
-        <v>81717.313032891761</v>
-      </c>
-      <c r="I33" s="230">
+        <v>53582.66</v>
+      </c>
+      <c r="I33" s="225">
         <f>E33-G33</f>
-        <v>103227.02696710826</v>
-      </c>
-      <c r="J33" s="231"/>
+        <v>171314.17</v>
+      </c>
+      <c r="J33" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5297,23 +5298,17 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
+++ b/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D940FCAB-2447-4936-AE42-6005C81BB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856416F9-A07C-4EC0-AAD5-244DD0DD8D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1422,129 +1422,6 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1555,10 +1432,133 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1993,12 +1993,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="192" t="s">
+      <c r="B3" s="197" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="193"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -2036,49 +2036,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="195" t="s">
+      <c r="B8" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="195"/>
+      <c r="C8" s="200"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="194" t="s">
+      <c r="A13" s="199" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
+      <c r="E13" s="199"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
+      <c r="A14" s="199"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="199"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
+      <c r="A15" s="199"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
-      <c r="B16" s="194"/>
-      <c r="C16" s="194"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="194"/>
+      <c r="A16" s="199"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="199"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2104,12 +2104,12 @@
       <c r="E21" s="99"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="190" t="s">
+      <c r="A22" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="191"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="37"/>
-      <c r="D22" s="230">
+      <c r="D22" s="189">
         <v>510846.85</v>
       </c>
       <c r="E22" s="174" t="s">
@@ -2118,12 +2118,12 @@
       <c r="H22" s="88"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="190" t="s">
+      <c r="A23" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="191"/>
+      <c r="B23" s="196"/>
       <c r="C23" s="37"/>
-      <c r="D23" s="230">
+      <c r="D23" s="189">
         <v>15000</v>
       </c>
       <c r="E23" s="102"/>
@@ -2151,12 +2151,12 @@
       <c r="E25" s="165"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="190" t="s">
+      <c r="A26" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="191"/>
+      <c r="B26" s="196"/>
       <c r="C26" s="39"/>
-      <c r="D26" s="232">
+      <c r="D26" s="191">
         <v>79864</v>
       </c>
       <c r="E26" s="104" t="s">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="229">
+      <c r="D30" s="188">
         <v>6403.1</v>
       </c>
       <c r="E30" s="174" t="str">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B31" s="115"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="229">
+      <c r="D31" s="188">
         <v>329815.06</v>
       </c>
       <c r="E31" s="104" t="s">
@@ -2223,12 +2223,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="188" t="s">
+      <c r="A32" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="189"/>
+      <c r="B32" s="194"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="229">
+      <c r="D32" s="188">
         <v>640644</v>
       </c>
       <c r="E32" s="104" t="s">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B33" s="101"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="229">
+      <c r="D33" s="188">
         <v>26036.19</v>
       </c>
       <c r="E33" s="104" t="s">
@@ -2268,12 +2268,12 @@
       <c r="E35" s="168"/>
     </row>
     <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="190" t="s">
+      <c r="A36" s="195" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="191"/>
+      <c r="B36" s="196"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="229">
+      <c r="D36" s="188">
         <v>82000</v>
       </c>
       <c r="E36" s="104" t="s">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B37" s="116"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="231">
+      <c r="D37" s="190">
         <v>150000</v>
       </c>
       <c r="E37" s="104" t="s">
@@ -2294,12 +2294,12 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="190" t="s">
+      <c r="A38" s="195" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="191"/>
+      <c r="B38" s="196"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="231">
+      <c r="D38" s="190">
         <v>500000</v>
       </c>
       <c r="E38" s="104" t="s">
@@ -2307,19 +2307,19 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="190" t="s">
+      <c r="A39" s="195" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="191"/>
+      <c r="B39" s="196"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="231">
+      <c r="D39" s="190">
         <v>157988.29</v>
       </c>
       <c r="E39" s="104"/>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="190"/>
-      <c r="B40" s="191"/>
+      <c r="A40" s="195"/>
+      <c r="B40" s="196"/>
       <c r="C40" s="5"/>
       <c r="D40" s="186"/>
       <c r="E40" s="104"/>
@@ -2346,12 +2346,12 @@
       <c r="E42" s="169"/>
     </row>
     <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="190" t="s">
+      <c r="A43" s="195" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="191"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="37"/>
-      <c r="D43" s="233">
+      <c r="D43" s="192">
         <v>170000</v>
       </c>
       <c r="E43" s="170" t="s">
@@ -2385,18 +2385,18 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="229">
+      <c r="D46" s="188">
         <v>69000</v>
       </c>
       <c r="E46" s="171"/>
     </row>
     <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="234" t="s">
+      <c r="A47" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="235"/>
+      <c r="B47" s="205"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="229">
+      <c r="D47" s="188">
         <v>14770</v>
       </c>
       <c r="E47" s="171"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="229">
+      <c r="D48" s="188">
         <v>56522.84</v>
       </c>
       <c r="E48" s="172"/>
@@ -2486,8 +2486,8 @@
       <c r="E57" s="71"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="198"/>
-      <c r="B58" s="198"/>
+      <c r="A58" s="203"/>
+      <c r="B58" s="203"/>
       <c r="C58" s="5"/>
       <c r="D58" s="103"/>
       <c r="E58" s="71"/>
@@ -2600,6 +2600,7 @@
         <f>-B69</f>
         <v>-2808890.3299999996</v>
       </c>
+      <c r="E75" s="29"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="39" t="s">
@@ -2686,14 +2687,8 @@
         <v>24</v>
       </c>
       <c r="B85" s="111"/>
-      <c r="E85" s="29">
-        <f>B86+B79</f>
-        <v>850965.62000000244</v>
-      </c>
-      <c r="F85">
-        <f>1006974.16-20000</f>
-        <v>986974.16</v>
-      </c>
+      <c r="E85" s="29"/>
+      <c r="F85" s="28"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="93" t="s">
@@ -2703,10 +2698,7 @@
         <f>SUM(B81:C85)</f>
         <v>1000000</v>
       </c>
-      <c r="F86" s="29">
-        <f>F85-E85</f>
-        <v>136008.53999999759</v>
-      </c>
+      <c r="F86" s="29"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="91"/>
@@ -2746,16 +2738,16 @@
     </row>
     <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="197" t="s">
+      <c r="A94" s="202" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="197"/>
-      <c r="C94" s="197"/>
+      <c r="B94" s="202"/>
+      <c r="C94" s="202"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="197"/>
-      <c r="B95" s="197"/>
-      <c r="C95" s="197"/>
+      <c r="A95" s="202"/>
+      <c r="B95" s="202"/>
+      <c r="C95" s="202"/>
     </row>
     <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="85"/>
@@ -2785,32 +2777,32 @@
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="196"/>
-      <c r="B100" s="196"/>
-      <c r="C100" s="196"/>
-      <c r="D100" s="196"/>
-      <c r="E100" s="196"/>
+      <c r="A100" s="201"/>
+      <c r="B100" s="201"/>
+      <c r="C100" s="201"/>
+      <c r="D100" s="201"/>
+      <c r="E100" s="201"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="196"/>
-      <c r="B101" s="196"/>
-      <c r="C101" s="196"/>
-      <c r="D101" s="196"/>
-      <c r="E101" s="196"/>
+      <c r="A101" s="201"/>
+      <c r="B101" s="201"/>
+      <c r="C101" s="201"/>
+      <c r="D101" s="201"/>
+      <c r="E101" s="201"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="196"/>
-      <c r="B102" s="196"/>
-      <c r="C102" s="196"/>
-      <c r="D102" s="196"/>
-      <c r="E102" s="196"/>
+      <c r="A102" s="201"/>
+      <c r="B102" s="201"/>
+      <c r="C102" s="201"/>
+      <c r="D102" s="201"/>
+      <c r="E102" s="201"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="196"/>
-      <c r="B103" s="196"/>
-      <c r="C103" s="196"/>
-      <c r="D103" s="196"/>
-      <c r="E103" s="196"/>
+      <c r="A103" s="201"/>
+      <c r="B103" s="201"/>
+      <c r="C103" s="201"/>
+      <c r="D103" s="201"/>
+      <c r="E103" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2867,16 +2859,16 @@
       <c r="B1" s="130"/>
       <c r="C1" s="131"/>
       <c r="D1" s="131"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
       <c r="O1" s="130"/>
       <c r="P1" s="132"/>
     </row>
@@ -2927,209 +2919,209 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="217" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="211"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="212"/>
+      <c r="B4" s="218"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="219"/>
       <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="213"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
-      <c r="E5" s="214"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="214"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="214"/>
-      <c r="L5" s="214"/>
-      <c r="M5" s="214"/>
-      <c r="N5" s="214"/>
-      <c r="O5" s="214"/>
-      <c r="P5" s="215"/>
+      <c r="A5" s="220"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="221"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="221"/>
+      <c r="M5" s="221"/>
+      <c r="N5" s="221"/>
+      <c r="O5" s="221"/>
+      <c r="P5" s="222"/>
       <c r="Q5" s="20"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="213"/>
-      <c r="B6" s="214"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="214"/>
-      <c r="F6" s="214"/>
-      <c r="G6" s="214"/>
-      <c r="H6" s="214"/>
-      <c r="I6" s="214"/>
-      <c r="J6" s="214"/>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="214"/>
-      <c r="N6" s="214"/>
-      <c r="O6" s="214"/>
-      <c r="P6" s="215"/>
+      <c r="A6" s="220"/>
+      <c r="B6" s="221"/>
+      <c r="C6" s="221"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="221"/>
+      <c r="F6" s="221"/>
+      <c r="G6" s="221"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
+      <c r="O6" s="221"/>
+      <c r="P6" s="222"/>
       <c r="Q6" s="20"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="213"/>
-      <c r="B7" s="214"/>
-      <c r="C7" s="214"/>
-      <c r="D7" s="214"/>
-      <c r="E7" s="214"/>
-      <c r="F7" s="214"/>
-      <c r="G7" s="214"/>
-      <c r="H7" s="214"/>
-      <c r="I7" s="214"/>
-      <c r="J7" s="214"/>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="215"/>
+      <c r="A7" s="220"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="221"/>
+      <c r="J7" s="221"/>
+      <c r="K7" s="221"/>
+      <c r="L7" s="221"/>
+      <c r="M7" s="221"/>
+      <c r="N7" s="221"/>
+      <c r="O7" s="221"/>
+      <c r="P7" s="222"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="216"/>
-      <c r="B8" s="217"/>
-      <c r="C8" s="217"/>
-      <c r="D8" s="217"/>
-      <c r="E8" s="217"/>
-      <c r="F8" s="217"/>
-      <c r="G8" s="217"/>
-      <c r="H8" s="217"/>
-      <c r="I8" s="217"/>
-      <c r="J8" s="217"/>
-      <c r="K8" s="217"/>
-      <c r="L8" s="217"/>
-      <c r="M8" s="217"/>
-      <c r="N8" s="217"/>
-      <c r="O8" s="217"/>
-      <c r="P8" s="218"/>
+      <c r="A8" s="223"/>
+      <c r="B8" s="224"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="224"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="224"/>
+      <c r="K8" s="224"/>
+      <c r="L8" s="224"/>
+      <c r="M8" s="224"/>
+      <c r="N8" s="224"/>
+      <c r="O8" s="224"/>
+      <c r="P8" s="225"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="221" t="s">
+      <c r="A9" s="228" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
-      <c r="M9" s="222"/>
-      <c r="N9" s="222"/>
-      <c r="O9" s="222"/>
-      <c r="P9" s="222"/>
+      <c r="B9" s="229"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="229"/>
+      <c r="P9" s="229"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="223" t="s">
+      <c r="A10" s="230" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
-      <c r="K10" s="223"/>
-      <c r="L10" s="223"/>
-      <c r="M10" s="223"/>
-      <c r="N10" s="223"/>
-      <c r="O10" s="223"/>
-      <c r="P10" s="223"/>
+      <c r="B10" s="230"/>
+      <c r="C10" s="230"/>
+      <c r="D10" s="230"/>
+      <c r="E10" s="230"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="230"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="230"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="230"/>
+      <c r="N10" s="230"/>
+      <c r="O10" s="230"/>
+      <c r="P10" s="230"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="204" t="s">
+      <c r="A11" s="211" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="112"/>
-      <c r="C11" s="204" t="s">
+      <c r="C11" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="204" t="s">
+      <c r="D11" s="211" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="204" t="s">
+      <c r="E11" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="200" t="s">
+      <c r="F11" s="207" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="204" t="s">
+      <c r="G11" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="206" t="s">
+      <c r="H11" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="200" t="s">
+      <c r="I11" s="207" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="200" t="s">
+      <c r="J11" s="207" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="208" t="s">
+      <c r="K11" s="215" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="200" t="s">
+      <c r="L11" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="200" t="s">
+      <c r="M11" s="207" t="s">
         <v>128</v>
       </c>
       <c r="N11" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="202" t="s">
+      <c r="O11" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="219" t="s">
+      <c r="P11" s="226" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="212"/>
       <c r="B12" s="113"/>
-      <c r="C12" s="205"/>
-      <c r="D12" s="224"/>
-      <c r="E12" s="205"/>
-      <c r="F12" s="201"/>
-      <c r="G12" s="205"/>
-      <c r="H12" s="207"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="209"/>
-      <c r="L12" s="201"/>
-      <c r="M12" s="201"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="208"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="214"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="216"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="208"/>
       <c r="N12" s="41" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O12" s="203"/>
-      <c r="P12" s="220"/>
+      <c r="O12" s="210"/>
+      <c r="P12" s="227"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44">
@@ -3657,18 +3649,20 @@
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="176"/>
+      <c r="M21" s="176">
+        <v>50000</v>
+      </c>
       <c r="N21" s="159">
         <f t="shared" si="4"/>
-        <v>130013.09</v>
+        <v>180013.09</v>
       </c>
       <c r="O21" s="57">
         <f t="shared" si="5"/>
-        <v>137814.09</v>
+        <v>190814.09</v>
       </c>
       <c r="P21" s="58">
         <f t="shared" si="6"/>
-        <v>133913.09</v>
+        <v>185413.09</v>
       </c>
       <c r="Q21" s="29">
         <f t="shared" si="7"/>
@@ -4405,7 +4399,7 @@
         <v>7200.22</v>
       </c>
       <c r="G34" s="151">
-        <f t="shared" ref="G28:G34" si="9">F34</f>
+        <f t="shared" ref="G34" si="9">F34</f>
         <v>7200.22</v>
       </c>
       <c r="H34" s="56">
@@ -4541,15 +4535,15 @@
       <c r="M36" s="66"/>
       <c r="N36" s="66">
         <f>SUM(N13:N35)</f>
-        <v>2548576.7600000012</v>
+        <v>2598576.7600000012</v>
       </c>
       <c r="O36" s="66">
         <f t="shared" si="10"/>
-        <v>2647219.7100000009</v>
+        <v>2700219.7100000009</v>
       </c>
       <c r="P36" s="66">
         <f>SUM(P13:P35)</f>
-        <v>2625033.7600000012</v>
+        <v>2676533.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4558,91 +4552,91 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="196" t="str">
+      <c r="C39" s="201" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="196"/>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="196"/>
-      <c r="I39" s="196"/>
-      <c r="J39" s="196"/>
-      <c r="K39" s="196"/>
-      <c r="L39" s="196"/>
-      <c r="M39" s="196"/>
-      <c r="N39" s="196"/>
+      <c r="D39" s="201"/>
+      <c r="E39" s="201"/>
+      <c r="F39" s="201"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="201"/>
+      <c r="I39" s="201"/>
+      <c r="J39" s="201"/>
+      <c r="K39" s="201"/>
+      <c r="L39" s="201"/>
+      <c r="M39" s="201"/>
+      <c r="N39" s="201"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="196"/>
-      <c r="D40" s="196"/>
-      <c r="E40" s="196"/>
-      <c r="F40" s="196"/>
-      <c r="G40" s="196"/>
-      <c r="H40" s="196"/>
-      <c r="I40" s="196"/>
-      <c r="J40" s="196"/>
-      <c r="K40" s="196"/>
-      <c r="L40" s="196"/>
-      <c r="M40" s="196"/>
-      <c r="N40" s="196"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="201"/>
+      <c r="F40" s="201"/>
+      <c r="G40" s="201"/>
+      <c r="H40" s="201"/>
+      <c r="I40" s="201"/>
+      <c r="J40" s="201"/>
+      <c r="K40" s="201"/>
+      <c r="L40" s="201"/>
+      <c r="M40" s="201"/>
+      <c r="N40" s="201"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="196"/>
-      <c r="D41" s="196"/>
-      <c r="E41" s="196"/>
-      <c r="F41" s="196"/>
-      <c r="G41" s="196"/>
-      <c r="H41" s="196"/>
-      <c r="I41" s="196"/>
-      <c r="J41" s="196"/>
-      <c r="K41" s="196"/>
-      <c r="L41" s="196"/>
-      <c r="M41" s="196"/>
-      <c r="N41" s="196"/>
+      <c r="C41" s="201"/>
+      <c r="D41" s="201"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="201"/>
+      <c r="G41" s="201"/>
+      <c r="H41" s="201"/>
+      <c r="I41" s="201"/>
+      <c r="J41" s="201"/>
+      <c r="K41" s="201"/>
+      <c r="L41" s="201"/>
+      <c r="M41" s="201"/>
+      <c r="N41" s="201"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="196"/>
-      <c r="D42" s="196"/>
-      <c r="E42" s="196"/>
-      <c r="F42" s="196"/>
-      <c r="G42" s="196"/>
-      <c r="H42" s="196"/>
-      <c r="I42" s="196"/>
-      <c r="J42" s="196"/>
-      <c r="K42" s="196"/>
-      <c r="L42" s="196"/>
-      <c r="M42" s="196"/>
-      <c r="N42" s="196"/>
+      <c r="C42" s="201"/>
+      <c r="D42" s="201"/>
+      <c r="E42" s="201"/>
+      <c r="F42" s="201"/>
+      <c r="G42" s="201"/>
+      <c r="H42" s="201"/>
+      <c r="I42" s="201"/>
+      <c r="J42" s="201"/>
+      <c r="K42" s="201"/>
+      <c r="L42" s="201"/>
+      <c r="M42" s="201"/>
+      <c r="N42" s="201"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="196"/>
-      <c r="D43" s="196"/>
-      <c r="E43" s="196"/>
-      <c r="F43" s="196"/>
-      <c r="G43" s="196"/>
-      <c r="H43" s="196"/>
-      <c r="I43" s="196"/>
-      <c r="J43" s="196"/>
-      <c r="K43" s="196"/>
-      <c r="L43" s="196"/>
-      <c r="M43" s="196"/>
-      <c r="N43" s="196"/>
+      <c r="C43" s="201"/>
+      <c r="D43" s="201"/>
+      <c r="E43" s="201"/>
+      <c r="F43" s="201"/>
+      <c r="G43" s="201"/>
+      <c r="H43" s="201"/>
+      <c r="I43" s="201"/>
+      <c r="J43" s="201"/>
+      <c r="K43" s="201"/>
+      <c r="L43" s="201"/>
+      <c r="M43" s="201"/>
+      <c r="N43" s="201"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="196"/>
-      <c r="D44" s="196"/>
-      <c r="E44" s="196"/>
-      <c r="F44" s="196"/>
-      <c r="G44" s="196"/>
-      <c r="H44" s="196"/>
-      <c r="I44" s="196"/>
-      <c r="J44" s="196"/>
-      <c r="K44" s="196"/>
-      <c r="L44" s="196"/>
-      <c r="M44" s="196"/>
-      <c r="N44" s="196"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="201"/>
+      <c r="G44" s="201"/>
+      <c r="H44" s="201"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="201"/>
+      <c r="L44" s="201"/>
+      <c r="M44" s="201"/>
+      <c r="N44" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4697,18 +4691,18 @@
       <c r="G3" s="150" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="227" t="s">
+      <c r="I3" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="228"/>
+      <c r="J3" s="235"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="119"/>
       <c r="C4" s="119"/>
       <c r="E4" s="119"/>
       <c r="G4" s="122"/>
-      <c r="I4" s="227"/>
-      <c r="J4" s="228"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="235"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="119">
@@ -4725,11 +4719,11 @@
         <f>E5</f>
         <v>8123.99</v>
       </c>
-      <c r="I5" s="225">
+      <c r="I5" s="232">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="226"/>
+      <c r="J5" s="233"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="119">
@@ -4745,11 +4739,11 @@
       <c r="G6" s="179">
         <v>0</v>
       </c>
-      <c r="I6" s="225">
+      <c r="I6" s="232">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
         <v>102901.79</v>
       </c>
-      <c r="J6" s="226"/>
+      <c r="J6" s="233"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="119">
@@ -4765,11 +4759,11 @@
       <c r="G7" s="179">
         <v>0</v>
       </c>
-      <c r="I7" s="225">
+      <c r="I7" s="232">
         <f t="shared" si="0"/>
         <v>3655.79</v>
       </c>
-      <c r="J7" s="226"/>
+      <c r="J7" s="233"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="119">
@@ -4786,11 +4780,11 @@
         <f>E8</f>
         <v>3655.79</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="226"/>
+      <c r="J8" s="233"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="120">
@@ -4807,11 +4801,11 @@
         <f>E9</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="226"/>
+      <c r="J9" s="233"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="120">
@@ -4828,11 +4822,11 @@
         <f>E10</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I10" s="225">
+      <c r="I10" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="226"/>
+      <c r="J10" s="233"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="120">
@@ -4849,11 +4843,11 @@
         <f>E11</f>
         <v>3655.79</v>
       </c>
-      <c r="I11" s="225">
+      <c r="I11" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="226"/>
+      <c r="J11" s="233"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="120">
@@ -4870,11 +4864,11 @@
         <f>E12</f>
         <v>3655.79</v>
       </c>
-      <c r="I12" s="225">
+      <c r="I12" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="226"/>
+      <c r="J12" s="233"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="119">
@@ -4890,11 +4884,11 @@
       <c r="G13" s="179">
         <v>0</v>
       </c>
-      <c r="I13" s="225">
+      <c r="I13" s="232">
         <f t="shared" si="0"/>
         <v>63231.57</v>
       </c>
-      <c r="J13" s="226"/>
+      <c r="J13" s="233"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="120">
@@ -4909,14 +4903,14 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="179">
-        <f>E14</f>
+        <f t="shared" ref="G14:G19" si="1">E14</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I14" s="225">
+      <c r="I14" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="226"/>
+      <c r="J14" s="233"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="120">
@@ -4931,14 +4925,14 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="179">
-        <f>E15</f>
+        <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I15" s="225">
+      <c r="I15" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="226"/>
+      <c r="J15" s="233"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="119">
@@ -4953,14 +4947,14 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="179">
-        <f>E16</f>
+        <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I16" s="225">
+      <c r="I16" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="226"/>
+      <c r="J16" s="233"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="120">
@@ -4975,14 +4969,14 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="179">
-        <f>E17</f>
+        <f t="shared" si="1"/>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I17" s="225">
+      <c r="I17" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="226"/>
+      <c r="J17" s="233"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="119">
@@ -4997,14 +4991,14 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="179">
-        <f>E18</f>
+        <f t="shared" si="1"/>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I18" s="225">
+      <c r="I18" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="226"/>
+      <c r="J18" s="233"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="120">
@@ -5019,22 +5013,22 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="179">
-        <f>E19</f>
+        <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="226"/>
+      <c r="J19" s="233"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="119"/>
       <c r="C20" s="119"/>
       <c r="E20" s="119"/>
       <c r="G20" s="122"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="226"/>
+      <c r="I20" s="232"/>
+      <c r="J20" s="233"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="143" t="s">
@@ -5051,11 +5045,11 @@
         <f>SUM(G5:G20)</f>
         <v>52399.68</v>
       </c>
-      <c r="I21" s="225">
+      <c r="I21" s="232">
         <f>E21-G21</f>
         <v>169789.15000000002</v>
       </c>
-      <c r="J21" s="226"/>
+      <c r="J21" s="233"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="119" t="s">
@@ -5070,11 +5064,11 @@
       <c r="G22" s="127">
         <v>207.02</v>
       </c>
-      <c r="I22" s="225">
-        <f t="shared" ref="I22" si="1">E22-G22</f>
+      <c r="I22" s="232">
+        <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>266.88</v>
       </c>
-      <c r="J22" s="226"/>
+      <c r="J22" s="233"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="119" t="s">
@@ -5089,11 +5083,11 @@
       <c r="G23" s="127">
         <v>177.45</v>
       </c>
-      <c r="I23" s="225">
-        <f t="shared" ref="I23:I31" si="2">E23-G23</f>
+      <c r="I23" s="232">
+        <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>228.75</v>
       </c>
-      <c r="J23" s="226"/>
+      <c r="J23" s="233"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="119" t="s">
@@ -5109,11 +5103,11 @@
       <c r="G24" s="127">
         <v>177.45</v>
       </c>
-      <c r="I24" s="225">
-        <f t="shared" si="2"/>
+      <c r="I24" s="232">
+        <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J24" s="226"/>
+      <c r="J24" s="233"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="119" t="s">
@@ -5129,11 +5123,11 @@
       <c r="G25" s="127">
         <v>177.45</v>
       </c>
-      <c r="I25" s="225">
-        <f t="shared" si="2"/>
+      <c r="I25" s="232">
+        <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J25" s="226"/>
+      <c r="J25" s="233"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="119" t="s">
@@ -5149,11 +5143,11 @@
       <c r="G26" s="127">
         <v>177.45</v>
       </c>
-      <c r="I26" s="225">
-        <f t="shared" si="2"/>
+      <c r="I26" s="232">
+        <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J26" s="226"/>
+      <c r="J26" s="233"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="119" t="s">
@@ -5168,11 +5162,11 @@
       <c r="G27" s="127">
         <v>88.72</v>
       </c>
-      <c r="I27" s="225">
-        <f t="shared" si="2"/>
+      <c r="I27" s="232">
+        <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J27" s="226"/>
+      <c r="J27" s="233"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="119" t="s">
@@ -5188,11 +5182,11 @@
       <c r="G28" s="127">
         <v>88.72</v>
       </c>
-      <c r="I28" s="225">
-        <f t="shared" si="2"/>
+      <c r="I28" s="232">
+        <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J28" s="226"/>
+      <c r="J28" s="233"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="119" t="s">
@@ -5208,11 +5202,11 @@
       <c r="G29" s="127">
         <v>88.72</v>
       </c>
-      <c r="I29" s="225">
-        <f t="shared" si="2"/>
+      <c r="I29" s="232">
+        <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J29" s="226"/>
+      <c r="J29" s="233"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="148" t="s">
@@ -5229,26 +5223,26 @@
         <f>SUM(G22:G29)</f>
         <v>1182.9800000000002</v>
       </c>
-      <c r="I30" s="225">
-        <f t="shared" si="2"/>
+      <c r="I30" s="232">
+        <f t="shared" si="3"/>
         <v>1525.0199999999993</v>
       </c>
-      <c r="J30" s="226"/>
+      <c r="J30" s="233"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E31" s="126"/>
       <c r="G31" s="123"/>
-      <c r="I31" s="225">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="226"/>
+      <c r="I31" s="232">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="233"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E32" s="124"/>
       <c r="G32" s="125"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="226"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="233"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E33" s="126">
@@ -5259,11 +5253,11 @@
         <f>G21+G30</f>
         <v>53582.66</v>
       </c>
-      <c r="I33" s="225">
+      <c r="I33" s="232">
         <f>E33-G33</f>
         <v>171314.17</v>
       </c>
-      <c r="J33" s="226"/>
+      <c r="J33" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
+++ b/2026/SALTA 1167/Junio/SALTA1167-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856416F9-A07C-4EC0-AAD5-244DD0DD8D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50852553-ACEA-4FA4-92A6-CACC23D6591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1431,18 +1426,33 @@
     <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1455,42 +1465,30 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1544,9 +1542,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1638,9 +1633,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1678,9 +1673,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1713,26 +1708,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1765,26 +1743,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1959,21 +1920,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="49" t="s">
         <v>74</v>
@@ -1982,7 +1943,7 @@
       <c r="D1" s="49"/>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="51" t="s">
         <v>14</v>
@@ -1991,16 +1952,16 @@
       <c r="D2" s="51"/>
       <c r="E2" s="52"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="203"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2011,7 +1972,7 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>75</v>
       </c>
@@ -2024,7 +1985,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>126</v>
       </c>
@@ -2035,57 +1996,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="200"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="199" t="s">
+      <c r="C8" s="205"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="204" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="199"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="199"/>
-      <c r="E13" s="199"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="199"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="199"/>
-      <c r="D14" s="199"/>
-      <c r="E14" s="199"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="199"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="199"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="199"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="199"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>104</v>
       </c>
@@ -2094,7 +2055,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>77</v>
       </c>
@@ -2103,11 +2064,11 @@
       <c r="D21" s="108"/>
       <c r="E21" s="99"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="195" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="196" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="196"/>
+      <c r="B22" s="197"/>
       <c r="C22" s="37"/>
       <c r="D22" s="189">
         <v>510846.85</v>
@@ -2117,11 +2078,11 @@
       </c>
       <c r="H22" s="88"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="195" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="196" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="196"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="37"/>
       <c r="D23" s="189">
         <v>15000</v>
@@ -2129,7 +2090,7 @@
       <c r="E23" s="102"/>
       <c r="H23" s="88"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
@@ -2141,7 +2102,7 @@
         <v>525846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>17</v>
       </c>
@@ -2150,11 +2111,11 @@
       <c r="D25" s="182"/>
       <c r="E25" s="165"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="195" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="196"/>
+      <c r="B26" s="197"/>
       <c r="C26" s="39"/>
       <c r="D26" s="191">
         <v>79864</v>
@@ -2163,7 +2124,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
@@ -2175,7 +2136,7 @@
         <v>79864</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
         <v>10</v>
       </c>
@@ -2184,7 +2145,7 @@
       <c r="D28" s="183"/>
       <c r="E28" s="166"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>67</v>
       </c>
@@ -2195,7 +2156,7 @@
       </c>
       <c r="E29" s="174"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>66</v>
       </c>
@@ -2209,7 +2170,7 @@
         <v>Transf 02/06</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>66</v>
       </c>
@@ -2222,11 +2183,11 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="193" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="200" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="194"/>
+      <c r="B32" s="201"/>
       <c r="C32" s="5"/>
       <c r="D32" s="188">
         <v>640644</v>
@@ -2235,7 +2196,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="105" t="s">
         <v>78</v>
       </c>
@@ -2248,7 +2209,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
@@ -2260,18 +2221,18 @@
         <v>1002898.3499999999</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="24"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="181"/>
       <c r="E35" s="168"/>
     </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="195" t="s">
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="196"/>
+      <c r="B36" s="197"/>
       <c r="C36" s="5"/>
       <c r="D36" s="188">
         <v>82000</v>
@@ -2280,7 +2241,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="173" t="s">
         <v>135</v>
       </c>
@@ -2293,11 +2254,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="195" t="s">
+    <row r="38" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="196" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="196"/>
+      <c r="B38" s="197"/>
       <c r="C38" s="5"/>
       <c r="D38" s="190">
         <v>500000</v>
@@ -2306,25 +2267,25 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="195" t="s">
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="196" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="196"/>
+      <c r="B39" s="197"/>
       <c r="C39" s="5"/>
       <c r="D39" s="190">
         <v>157988.29</v>
       </c>
       <c r="E39" s="104"/>
     </row>
-    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="195"/>
-      <c r="B40" s="196"/>
+    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="196"/>
+      <c r="B40" s="197"/>
       <c r="C40" s="5"/>
       <c r="D40" s="186"/>
       <c r="E40" s="104"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>6</v>
       </c>
@@ -2336,7 +2297,7 @@
         <v>889988.29</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
         <v>11</v>
       </c>
@@ -2345,11 +2306,11 @@
       <c r="D42" s="187"/>
       <c r="E42" s="169"/>
     </row>
-    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="195" t="s">
+    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="196" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="196"/>
+      <c r="B43" s="197"/>
       <c r="C43" s="37"/>
       <c r="D43" s="192">
         <v>170000</v>
@@ -2358,7 +2319,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
         <v>9</v>
       </c>
@@ -2370,7 +2331,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2340,7 @@
       <c r="D45" s="107"/>
       <c r="E45" s="117"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>26</v>
       </c>
@@ -2390,18 +2351,18 @@
       </c>
       <c r="E46" s="171"/>
     </row>
-    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="204" t="s">
+    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="198" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="205"/>
+      <c r="B47" s="199"/>
       <c r="C47" s="5"/>
       <c r="D47" s="188">
         <v>14770</v>
       </c>
       <c r="E47" s="171"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>116</v>
       </c>
@@ -2412,7 +2373,7 @@
       </c>
       <c r="E48" s="172"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="36" t="s">
         <v>9</v>
       </c>
@@ -2424,14 +2385,14 @@
         <v>140292.84</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="70"/>
       <c r="E50" s="76"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>100</v>
       </c>
@@ -2440,13 +2401,13 @@
       <c r="D51" s="77"/>
       <c r="E51" s="118"/>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="D52" s="78"/>
       <c r="E52" s="79"/>
       <c r="F52" s="29"/>
     </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>96</v>
       </c>
@@ -2460,16 +2421,16 @@
       <c r="F53" s="98"/>
       <c r="G53" s="29"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D54" s="78"/>
       <c r="E54" s="78"/>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D55" s="78"/>
       <c r="E55" s="78"/>
       <c r="H55" s="110"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>97</v>
       </c>
@@ -2478,35 +2439,35 @@
       <c r="D56" s="82"/>
       <c r="E56" s="83"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72"/>
       <c r="B57" s="101"/>
       <c r="C57" s="5"/>
       <c r="D57" s="73"/>
       <c r="E57" s="71"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="203"/>
-      <c r="B58" s="203"/>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="195"/>
+      <c r="B58" s="195"/>
       <c r="C58" s="5"/>
       <c r="D58" s="103"/>
       <c r="E58" s="71"/>
     </row>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="72"/>
       <c r="B60" s="74"/>
       <c r="C60" s="5"/>
       <c r="D60" s="73"/>
       <c r="E60" s="71"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="34"/>
       <c r="B61" s="33"/>
       <c r="C61" s="33"/>
@@ -2516,9 +2477,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>99</v>
       </c>
@@ -2527,8 +2488,8 @@
       <c r="D64" s="23"/>
       <c r="E64" s="161"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>98</v>
       </c>
@@ -2540,8 +2501,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="68" t="s">
         <v>105</v>
       </c>
@@ -2550,7 +2511,7 @@
         <v>2808890.3299999996</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="68" t="s">
         <v>106</v>
       </c>
@@ -2559,7 +2520,7 @@
         <v>2808890.3299999996</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="68" t="s">
         <v>107</v>
       </c>
@@ -2568,7 +2529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="68" t="s">
         <v>108</v>
       </c>
@@ -2577,12 +2538,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73"/>
       <c r="B73" s="28"/>
       <c r="C73" s="26"/>
     </row>
-    <row r="74" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="90" t="s">
         <v>109</v>
       </c>
@@ -2592,7 +2553,7 @@
       <c r="C74" s="26"/>
       <c r="D74" s="32"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="39" t="s">
         <v>102</v>
       </c>
@@ -2602,7 +2563,7 @@
       </c>
       <c r="E75" s="29"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="39" t="s">
         <v>25</v>
       </c>
@@ -2611,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="39" t="s">
         <v>111</v>
       </c>
@@ -2620,13 +2581,13 @@
         <v>2367966.9600000004</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="97" t="s">
         <v>24</v>
       </c>
       <c r="B78" s="111"/>
     </row>
-    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="93" t="s">
         <v>113</v>
       </c>
@@ -2636,13 +2597,13 @@
       </c>
       <c r="D79" s="29"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="91"/>
       <c r="B80" s="91"/>
       <c r="D80" s="29"/>
       <c r="E80" s="28"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="90" t="s">
         <v>110</v>
       </c>
@@ -2652,7 +2613,7 @@
       <c r="D81" s="28"/>
       <c r="E81" s="29"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="39" t="s">
         <v>103</v>
       </c>
@@ -2663,7 +2624,7 @@
       <c r="D82" s="29"/>
       <c r="E82" s="29"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="39" t="s">
         <v>25</v>
       </c>
@@ -2673,7 +2634,7 @@
       </c>
       <c r="D83" s="29"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="39" t="s">
         <v>112</v>
       </c>
@@ -2682,7 +2643,7 @@
       </c>
       <c r="D84" s="162"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="97" t="s">
         <v>24</v>
       </c>
@@ -2690,7 +2651,7 @@
       <c r="E85" s="29"/>
       <c r="F85" s="28"/>
     </row>
-    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="93" t="s">
         <v>114</v>
       </c>
@@ -2700,15 +2661,15 @@
       </c>
       <c r="F86" s="29"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="91"/>
       <c r="B87" s="91"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="91"/>
       <c r="B88" s="91"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="90" t="s">
         <v>129</v>
       </c>
@@ -2716,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="39" t="s">
         <v>130</v>
       </c>
@@ -2724,11 +2685,11 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="97"/>
       <c r="B91" s="111"/>
     </row>
-    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="93" t="s">
         <v>145</v>
       </c>
@@ -2736,20 +2697,20 @@
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="202" t="s">
+    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="194" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="202"/>
-      <c r="C94" s="202"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="202"/>
-      <c r="B95" s="202"/>
-      <c r="C95" s="202"/>
-    </row>
-    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="194"/>
+      <c r="C94" s="194"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="194"/>
+      <c r="B95" s="194"/>
+      <c r="C95" s="194"/>
+    </row>
+    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="85"/>
       <c r="B96" s="25"/>
       <c r="C96" s="25">
@@ -2757,13 +2718,13 @@
       </c>
       <c r="E96" s="98"/>
     </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="85"/>
       <c r="B97" s="87"/>
       <c r="C97" s="84"/>
       <c r="D97" s="98"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="30" t="s">
         <v>6</v>
       </c>
@@ -2773,39 +2734,46 @@
       </c>
       <c r="C98" s="31"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M99" s="6"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="201"/>
-      <c r="B100" s="201"/>
-      <c r="C100" s="201"/>
-      <c r="D100" s="201"/>
-      <c r="E100" s="201"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="201"/>
-      <c r="B101" s="201"/>
-      <c r="C101" s="201"/>
-      <c r="D101" s="201"/>
-      <c r="E101" s="201"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="201"/>
-      <c r="B102" s="201"/>
-      <c r="C102" s="201"/>
-      <c r="D102" s="201"/>
-      <c r="E102" s="201"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="201"/>
-      <c r="B103" s="201"/>
-      <c r="C103" s="201"/>
-      <c r="D103" s="201"/>
-      <c r="E103" s="201"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="193"/>
+      <c r="B100" s="193"/>
+      <c r="C100" s="193"/>
+      <c r="D100" s="193"/>
+      <c r="E100" s="193"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="193"/>
+      <c r="B101" s="193"/>
+      <c r="C101" s="193"/>
+      <c r="D101" s="193"/>
+      <c r="E101" s="193"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="193"/>
+      <c r="B102" s="193"/>
+      <c r="C102" s="193"/>
+      <c r="D102" s="193"/>
+      <c r="E102" s="193"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="193"/>
+      <c r="B103" s="193"/>
+      <c r="C103" s="193"/>
+      <c r="D103" s="193"/>
+      <c r="E103" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="A94:C95"/>
     <mergeCell ref="A58:B58"/>
@@ -2815,13 +2783,6 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2832,47 +2793,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="129"/>
       <c r="B1" s="130"/>
       <c r="C1" s="131"/>
       <c r="D1" s="131"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
       <c r="O1" s="130"/>
       <c r="P1" s="132"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
       <c r="B2" s="134"/>
       <c r="C2" s="135"/>
@@ -2890,7 +2851,7 @@
         <v>94</v>
       </c>
       <c r="K2" s="138">
-        <v>2400000</v>
+        <v>2700000</v>
       </c>
       <c r="L2" s="138"/>
       <c r="M2" s="138"/>
@@ -2899,7 +2860,7 @@
       <c r="P2" s="141"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="133"/>
       <c r="B3" s="134"/>
       <c r="C3" s="135"/>
@@ -2918,212 +2879,212 @@
       <c r="P3" s="141"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="217" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="218" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="219"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="219"/>
+      <c r="E4" s="219"/>
+      <c r="F4" s="219"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="219"/>
+      <c r="I4" s="219"/>
+      <c r="J4" s="219"/>
+      <c r="K4" s="219"/>
+      <c r="L4" s="219"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="220"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="220"/>
-      <c r="B5" s="221"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="221"/>
-      <c r="E5" s="221"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="221"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
-      <c r="M5" s="221"/>
-      <c r="N5" s="221"/>
-      <c r="O5" s="221"/>
-      <c r="P5" s="222"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
+      <c r="P5" s="223"/>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="220"/>
-      <c r="B6" s="221"/>
-      <c r="C6" s="221"/>
-      <c r="D6" s="221"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="221"/>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="221"/>
-      <c r="O6" s="221"/>
-      <c r="P6" s="222"/>
+    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="221"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="222"/>
+      <c r="N6" s="222"/>
+      <c r="O6" s="222"/>
+      <c r="P6" s="223"/>
       <c r="Q6" s="20"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="220"/>
-      <c r="B7" s="221"/>
-      <c r="C7" s="221"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="221"/>
-      <c r="H7" s="221"/>
-      <c r="I7" s="221"/>
-      <c r="J7" s="221"/>
-      <c r="K7" s="221"/>
-      <c r="L7" s="221"/>
-      <c r="M7" s="221"/>
-      <c r="N7" s="221"/>
-      <c r="O7" s="221"/>
-      <c r="P7" s="222"/>
+    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
+      <c r="M7" s="222"/>
+      <c r="N7" s="222"/>
+      <c r="O7" s="222"/>
+      <c r="P7" s="223"/>
       <c r="Q7" s="20"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="223"/>
-      <c r="B8" s="224"/>
-      <c r="C8" s="224"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="224"/>
-      <c r="F8" s="224"/>
-      <c r="G8" s="224"/>
-      <c r="H8" s="224"/>
-      <c r="I8" s="224"/>
-      <c r="J8" s="224"/>
-      <c r="K8" s="224"/>
-      <c r="L8" s="224"/>
-      <c r="M8" s="224"/>
-      <c r="N8" s="224"/>
-      <c r="O8" s="224"/>
-      <c r="P8" s="225"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="228" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="224"/>
+      <c r="B8" s="225"/>
+      <c r="C8" s="225"/>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="226"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="229" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="229"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="229"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="230" t="s">
+      <c r="B9" s="230"/>
+      <c r="C9" s="230"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="230"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="230"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="230"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="230"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="230"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="230"/>
+      <c r="P9" s="230"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="231" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="230"/>
-      <c r="C10" s="230"/>
-      <c r="D10" s="230"/>
-      <c r="E10" s="230"/>
-      <c r="F10" s="230"/>
-      <c r="G10" s="230"/>
-      <c r="H10" s="230"/>
-      <c r="I10" s="230"/>
-      <c r="J10" s="230"/>
-      <c r="K10" s="230"/>
-      <c r="L10" s="230"/>
-      <c r="M10" s="230"/>
-      <c r="N10" s="230"/>
-      <c r="O10" s="230"/>
-      <c r="P10" s="230"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="211" t="s">
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="231"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="231"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="231"/>
+      <c r="O10" s="231"/>
+      <c r="P10" s="231"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="206" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="112"/>
-      <c r="C11" s="211" t="s">
+      <c r="C11" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="211" t="s">
+      <c r="D11" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="211" t="s">
+      <c r="E11" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="207" t="s">
+      <c r="F11" s="209" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="211" t="s">
+      <c r="G11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="213" t="s">
+      <c r="H11" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="207" t="s">
+      <c r="I11" s="209" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="207" t="s">
+      <c r="J11" s="209" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="215" t="s">
+      <c r="K11" s="216" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="207" t="s">
+      <c r="L11" s="209" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="207" t="s">
+      <c r="M11" s="209" t="s">
         <v>128</v>
       </c>
       <c r="N11" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="209" t="s">
+      <c r="O11" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="226" t="s">
+      <c r="P11" s="227" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="212"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="208"/>
       <c r="B12" s="113"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="208"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="214"/>
-      <c r="I12" s="208"/>
-      <c r="J12" s="208"/>
-      <c r="K12" s="216"/>
-      <c r="L12" s="208"/>
-      <c r="M12" s="208"/>
+      <c r="C12" s="208"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="208"/>
+      <c r="F12" s="210"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="215"/>
+      <c r="I12" s="210"/>
+      <c r="J12" s="210"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="210"/>
+      <c r="M12" s="210"/>
       <c r="N12" s="41" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O12" s="210"/>
-      <c r="P12" s="227"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="213"/>
+      <c r="P12" s="228"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="44">
         <v>1</v>
       </c>
@@ -3154,7 +3115,7 @@
       </c>
       <c r="J13" s="106">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
-        <v>288000</v>
+        <v>324000</v>
       </c>
       <c r="K13" s="106">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
@@ -3167,21 +3128,21 @@
       <c r="M13" s="176"/>
       <c r="N13" s="159">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>288000.01</v>
+        <v>324000.01</v>
       </c>
       <c r="O13" s="57">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>305280.01</v>
+        <v>343440.01</v>
       </c>
       <c r="P13" s="58">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>296640.01</v>
+        <v>333720.01</v>
       </c>
       <c r="Q13" s="29">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="152">
         <v>2</v>
       </c>
@@ -3211,7 +3172,7 @@
       </c>
       <c r="J14" s="156">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K14" s="156">
         <f t="shared" si="2"/>
@@ -3224,22 +3185,22 @@
       <c r="M14" s="177"/>
       <c r="N14" s="159">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>260717.02</v>
+        <v>280517.02</v>
       </c>
       <c r="O14" s="157">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>276360.02</v>
+        <v>297348.02</v>
       </c>
       <c r="P14" s="158">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>268539.02</v>
+        <v>288933.02</v>
       </c>
       <c r="Q14" s="29">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44">
         <v>3</v>
       </c>
@@ -3272,7 +3233,7 @@
       </c>
       <c r="J15" s="106">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K15" s="106">
         <f t="shared" si="2"/>
@@ -3285,22 +3246,22 @@
       <c r="M15" s="175"/>
       <c r="N15" s="159">
         <f t="shared" si="4"/>
-        <v>133256.03</v>
+        <v>149456.03</v>
       </c>
       <c r="O15" s="57">
         <f t="shared" si="5"/>
-        <v>141251.03</v>
+        <v>158423.03</v>
       </c>
       <c r="P15" s="58">
         <f t="shared" si="6"/>
-        <v>137254.03</v>
+        <v>153940.03</v>
       </c>
       <c r="Q15" s="29">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44">
         <v>4</v>
       </c>
@@ -3333,7 +3294,7 @@
       </c>
       <c r="J16" s="106">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K16" s="106">
         <f t="shared" si="2"/>
@@ -3346,22 +3307,22 @@
       <c r="M16" s="176"/>
       <c r="N16" s="159">
         <f t="shared" si="4"/>
-        <v>152800.04</v>
+        <v>172600.04</v>
       </c>
       <c r="O16" s="57">
         <f t="shared" si="5"/>
-        <v>161968.04</v>
+        <v>182956.04</v>
       </c>
       <c r="P16" s="58">
         <f t="shared" si="6"/>
-        <v>157384.04</v>
+        <v>177778.04</v>
       </c>
       <c r="Q16" s="29">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="152">
         <v>5</v>
       </c>
@@ -3394,7 +3355,7 @@
       </c>
       <c r="J17" s="156">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K17" s="156">
         <f t="shared" si="2"/>
@@ -3409,15 +3370,15 @@
       </c>
       <c r="N17" s="159">
         <f t="shared" si="4"/>
-        <v>158400.04999999999</v>
+        <v>178200.05</v>
       </c>
       <c r="O17" s="157">
         <f t="shared" si="5"/>
-        <v>167904.05</v>
+        <v>188892.05</v>
       </c>
       <c r="P17" s="158">
         <f t="shared" si="6"/>
-        <v>163152.04999999999</v>
+        <v>183546.05</v>
       </c>
       <c r="Q17" s="29">
         <f t="shared" si="7"/>
@@ -3427,7 +3388,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44">
         <v>6</v>
       </c>
@@ -3459,7 +3420,7 @@
       </c>
       <c r="J18" s="106">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K18" s="106">
         <f t="shared" si="2"/>
@@ -3472,22 +3433,22 @@
       <c r="M18" s="176"/>
       <c r="N18" s="159">
         <f t="shared" si="4"/>
-        <v>140724.06</v>
+        <v>156924.06</v>
       </c>
       <c r="O18" s="57">
         <f t="shared" si="5"/>
-        <v>149168.06</v>
+        <v>166340.06</v>
       </c>
       <c r="P18" s="58">
         <f t="shared" si="6"/>
-        <v>144946.06</v>
+        <v>161632.06</v>
       </c>
       <c r="Q18" s="29">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="152">
         <v>7</v>
       </c>
@@ -3517,7 +3478,7 @@
       </c>
       <c r="J19" s="156">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K19" s="156">
         <f t="shared" si="2"/>
@@ -3530,22 +3491,22 @@
       <c r="M19" s="176"/>
       <c r="N19" s="159">
         <f t="shared" si="4"/>
-        <v>263088.07</v>
+        <v>279288.07</v>
       </c>
       <c r="O19" s="157">
         <f t="shared" si="5"/>
-        <v>278873.07</v>
+        <v>296045.07</v>
       </c>
       <c r="P19" s="158">
         <f t="shared" si="6"/>
-        <v>270981.07</v>
+        <v>287667.07</v>
       </c>
       <c r="Q19" s="29">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="152">
         <v>8</v>
       </c>
@@ -3578,7 +3539,7 @@
       </c>
       <c r="J20" s="156">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K20" s="156">
         <f t="shared" si="2"/>
@@ -3591,22 +3552,22 @@
       <c r="M20" s="176"/>
       <c r="N20" s="159">
         <f t="shared" si="4"/>
-        <v>221632.08</v>
+        <v>241432.08</v>
       </c>
       <c r="O20" s="157">
         <f t="shared" si="5"/>
-        <v>234930.08</v>
+        <v>255918.07999999999</v>
       </c>
       <c r="P20" s="158">
         <f t="shared" si="6"/>
-        <v>228281.08</v>
+        <v>248675.08</v>
       </c>
       <c r="Q20" s="29">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44">
         <v>9</v>
       </c>
@@ -3639,7 +3600,7 @@
       </c>
       <c r="J21" s="106">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K21" s="106">
         <f t="shared" si="2"/>
@@ -3654,22 +3615,22 @@
       </c>
       <c r="N21" s="159">
         <f t="shared" si="4"/>
-        <v>180013.09</v>
+        <v>199813.09</v>
       </c>
       <c r="O21" s="57">
         <f t="shared" si="5"/>
-        <v>190814.09</v>
+        <v>211802.09</v>
       </c>
       <c r="P21" s="58">
         <f t="shared" si="6"/>
-        <v>185413.09</v>
+        <v>205807.09</v>
       </c>
       <c r="Q21" s="29">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44">
         <v>10</v>
       </c>
@@ -3702,7 +3663,7 @@
       </c>
       <c r="J22" s="106">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K22" s="106">
         <f t="shared" si="2"/>
@@ -3715,22 +3676,22 @@
       <c r="M22" s="176"/>
       <c r="N22" s="159">
         <f t="shared" si="4"/>
-        <v>-1.9</v>
+        <v>16198.1</v>
       </c>
       <c r="O22" s="57">
         <f t="shared" si="5"/>
-        <v>-1.9</v>
+        <v>17170.099999999999</v>
       </c>
       <c r="P22" s="58">
         <f t="shared" si="6"/>
-        <v>-1.9</v>
+        <v>16684.099999999999</v>
       </c>
       <c r="Q22" s="29">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44">
         <v>11</v>
       </c>
@@ -3761,7 +3722,7 @@
       </c>
       <c r="J23" s="106">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K23" s="106">
         <f t="shared" si="2"/>
@@ -3774,15 +3735,15 @@
       <c r="M23" s="176"/>
       <c r="N23" s="159">
         <f t="shared" si="4"/>
-        <v>129600.11</v>
+        <v>145800.10999999999</v>
       </c>
       <c r="O23" s="57">
         <f t="shared" si="5"/>
-        <v>137376.10999999999</v>
+        <v>154548.10999999999</v>
       </c>
       <c r="P23" s="58">
         <f t="shared" si="6"/>
-        <v>133488.10999999999</v>
+        <v>150174.10999999999</v>
       </c>
       <c r="Q23" s="29">
         <f t="shared" si="7"/>
@@ -3792,7 +3753,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44">
         <v>12</v>
       </c>
@@ -3825,7 +3786,7 @@
       </c>
       <c r="J24" s="106">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K24" s="106">
         <f t="shared" si="2"/>
@@ -3838,22 +3799,22 @@
       <c r="M24" s="176"/>
       <c r="N24" s="159">
         <f t="shared" si="4"/>
-        <v>158400.12</v>
+        <v>178200.12</v>
       </c>
       <c r="O24" s="57">
         <f t="shared" si="5"/>
-        <v>167904.12</v>
+        <v>188892.12</v>
       </c>
       <c r="P24" s="58">
         <f t="shared" si="6"/>
-        <v>163152.12</v>
+        <v>183546.12</v>
       </c>
       <c r="Q24" s="29">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44">
         <v>13</v>
       </c>
@@ -3885,7 +3846,7 @@
       </c>
       <c r="J25" s="106">
         <f t="shared" si="1"/>
-        <v>158400</v>
+        <v>178200</v>
       </c>
       <c r="K25" s="106">
         <f t="shared" si="2"/>
@@ -3898,22 +3859,22 @@
       <c r="M25" s="176"/>
       <c r="N25" s="159">
         <f t="shared" si="4"/>
-        <v>153779.13</v>
+        <v>173579.13</v>
       </c>
       <c r="O25" s="57">
         <f t="shared" si="5"/>
-        <v>163006.13</v>
+        <v>183994.13</v>
       </c>
       <c r="P25" s="58">
         <f t="shared" si="6"/>
-        <v>158392.13</v>
+        <v>178786.13</v>
       </c>
       <c r="Q25" s="29">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="152">
         <v>14</v>
       </c>
@@ -3944,7 +3905,7 @@
       </c>
       <c r="J26" s="156">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K26" s="156">
         <f t="shared" si="2"/>
@@ -3957,22 +3918,22 @@
       <c r="M26" s="177"/>
       <c r="N26" s="159">
         <f t="shared" si="4"/>
-        <v>129600.14</v>
+        <v>145800.14000000001</v>
       </c>
       <c r="O26" s="157">
         <f t="shared" si="5"/>
-        <v>137376.14000000001</v>
+        <v>154548.14000000001</v>
       </c>
       <c r="P26" s="158">
         <f t="shared" si="6"/>
-        <v>133488.14000000001</v>
+        <v>150174.14000000001</v>
       </c>
       <c r="Q26" s="29">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44">
         <v>15</v>
       </c>
@@ -4003,7 +3964,7 @@
       </c>
       <c r="J27" s="106">
         <f t="shared" si="1"/>
-        <v>129600</v>
+        <v>145800.00000000003</v>
       </c>
       <c r="K27" s="106">
         <f t="shared" si="2"/>
@@ -4016,22 +3977,22 @@
       <c r="M27" s="176"/>
       <c r="N27" s="159">
         <f t="shared" si="4"/>
-        <v>129600.15</v>
+        <v>145800.15</v>
       </c>
       <c r="O27" s="57">
         <f t="shared" si="5"/>
-        <v>137376.15</v>
+        <v>154548.15</v>
       </c>
       <c r="P27" s="58">
         <f t="shared" si="6"/>
-        <v>133488.15</v>
+        <v>150174.15</v>
       </c>
       <c r="Q27" s="29">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="152">
         <v>16</v>
       </c>
@@ -4063,7 +4024,7 @@
       </c>
       <c r="J28" s="106">
         <f t="shared" si="1"/>
-        <v>16800</v>
+        <v>18899.999999999996</v>
       </c>
       <c r="K28" s="106">
         <f t="shared" si="2"/>
@@ -4076,22 +4037,22 @@
       <c r="M28" s="176"/>
       <c r="N28" s="159">
         <f t="shared" si="4"/>
-        <v>18509.16</v>
+        <v>20609.16</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" si="5"/>
-        <v>19620.16</v>
+        <v>21846.16</v>
       </c>
       <c r="P28" s="58">
         <f t="shared" si="6"/>
-        <v>19064.16</v>
+        <v>21227.16</v>
       </c>
       <c r="Q28" s="29">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="152">
         <v>17</v>
       </c>
@@ -4122,7 +4083,7 @@
       </c>
       <c r="J29" s="106">
         <f t="shared" si="1"/>
-        <v>14400</v>
+        <v>16200</v>
       </c>
       <c r="K29" s="106">
         <f t="shared" si="2"/>
@@ -4135,22 +4096,22 @@
       <c r="M29" s="176"/>
       <c r="N29" s="159">
         <f t="shared" si="4"/>
-        <v>14629.17</v>
+        <v>16429.169999999998</v>
       </c>
       <c r="O29" s="57">
         <f t="shared" si="5"/>
-        <v>15507.17</v>
+        <v>17415.169999999998</v>
       </c>
       <c r="P29" s="58">
         <f t="shared" si="6"/>
-        <v>15068.17</v>
+        <v>16922.169999999998</v>
       </c>
       <c r="Q29" s="29">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44">
         <v>18</v>
       </c>
@@ -4181,7 +4142,7 @@
       </c>
       <c r="J30" s="106">
         <f t="shared" si="1"/>
-        <v>14400</v>
+        <v>16200</v>
       </c>
       <c r="K30" s="106">
         <f t="shared" si="2"/>
@@ -4194,22 +4155,22 @@
       <c r="M30" s="176"/>
       <c r="N30" s="159">
         <f t="shared" si="4"/>
-        <v>14629.18</v>
+        <v>16429.18</v>
       </c>
       <c r="O30" s="57">
         <f t="shared" si="5"/>
-        <v>15507.18</v>
+        <v>17415.18</v>
       </c>
       <c r="P30" s="58">
         <f t="shared" si="6"/>
-        <v>15068.18</v>
+        <v>16922.18</v>
       </c>
       <c r="Q30" s="29">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="152">
         <v>19</v>
       </c>
@@ -4240,7 +4201,7 @@
       </c>
       <c r="J31" s="156">
         <f t="shared" si="1"/>
-        <v>14400</v>
+        <v>16200</v>
       </c>
       <c r="K31" s="156">
         <f t="shared" si="2"/>
@@ -4253,19 +4214,19 @@
       <c r="M31" s="177"/>
       <c r="N31" s="159">
         <f t="shared" si="4"/>
-        <v>14629.19</v>
+        <v>16429.189999999999</v>
       </c>
       <c r="O31" s="157"/>
       <c r="P31" s="158">
         <f t="shared" si="6"/>
-        <v>15068.19</v>
+        <v>16922.189999999999</v>
       </c>
       <c r="Q31" s="29">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A32" s="59">
         <v>20</v>
       </c>
@@ -4298,7 +4259,7 @@
       </c>
       <c r="J32" s="106">
         <f t="shared" si="1"/>
-        <v>14400</v>
+        <v>16200</v>
       </c>
       <c r="K32" s="106">
         <f t="shared" si="2"/>
@@ -4311,19 +4272,19 @@
       <c r="M32" s="176"/>
       <c r="N32" s="159">
         <f t="shared" si="4"/>
-        <v>14629.2</v>
+        <v>16429.2</v>
       </c>
       <c r="O32" s="57"/>
       <c r="P32" s="58">
         <f t="shared" si="6"/>
-        <v>15068.2</v>
+        <v>16922.2</v>
       </c>
       <c r="Q32" s="29">
         <f t="shared" ref="Q32:Q35" si="8">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="59">
         <v>21</v>
       </c>
@@ -4356,7 +4317,7 @@
       </c>
       <c r="J33" s="106">
         <f t="shared" si="1"/>
-        <v>7200</v>
+        <v>8100</v>
       </c>
       <c r="K33" s="106">
         <f t="shared" si="2"/>
@@ -4369,19 +4330,19 @@
       <c r="M33" s="176"/>
       <c r="N33" s="159">
         <f t="shared" si="4"/>
-        <v>7314.21</v>
+        <v>8214.2099999999991</v>
       </c>
       <c r="O33" s="57"/>
       <c r="P33" s="58">
         <f t="shared" si="6"/>
-        <v>7533.21</v>
+        <v>8460.2099999999991</v>
       </c>
       <c r="Q33" s="29">
         <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="60">
         <v>22</v>
       </c>
@@ -4412,7 +4373,7 @@
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
-        <v>7200</v>
+        <v>8100</v>
       </c>
       <c r="K34" s="106">
         <f t="shared" si="2"/>
@@ -4425,19 +4386,19 @@
       <c r="M34" s="176"/>
       <c r="N34" s="159">
         <f t="shared" si="4"/>
-        <v>7314.22</v>
+        <v>8214.2199999999993</v>
       </c>
       <c r="O34" s="57"/>
       <c r="P34" s="58">
         <f t="shared" si="6"/>
-        <v>7533.22</v>
+        <v>8460.2199999999993</v>
       </c>
       <c r="Q34" s="29">
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="44">
         <v>23</v>
       </c>
@@ -4470,7 +4431,7 @@
       </c>
       <c r="J35" s="106">
         <f t="shared" si="1"/>
-        <v>7200</v>
+        <v>8100</v>
       </c>
       <c r="K35" s="106">
         <f t="shared" si="2"/>
@@ -4483,19 +4444,19 @@
       <c r="M35" s="176"/>
       <c r="N35" s="159">
         <f t="shared" si="4"/>
-        <v>7314.23</v>
+        <v>8214.23</v>
       </c>
       <c r="O35" s="63"/>
       <c r="P35" s="58">
         <f t="shared" si="6"/>
-        <v>7533.23</v>
+        <v>8460.23</v>
       </c>
       <c r="Q35" s="29">
         <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="64"/>
       <c r="B36" s="64"/>
       <c r="C36" s="65"/>
@@ -4522,7 +4483,7 @@
       </c>
       <c r="J36" s="92">
         <f t="shared" si="10"/>
-        <v>2400000</v>
+        <v>2700000</v>
       </c>
       <c r="K36" s="42">
         <f t="shared" si="10"/>
@@ -4535,117 +4496,111 @@
       <c r="M36" s="66"/>
       <c r="N36" s="66">
         <f>SUM(N13:N35)</f>
-        <v>2598576.7600000012</v>
+        <v>2898576.7600000012</v>
       </c>
       <c r="O36" s="66">
         <f t="shared" si="10"/>
-        <v>2700219.7100000009</v>
+        <v>3011541.7100000004</v>
       </c>
       <c r="P36" s="66">
         <f>SUM(P13:P35)</f>
-        <v>2676533.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2985533.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="201" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="193" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="201"/>
-      <c r="E39" s="201"/>
-      <c r="F39" s="201"/>
-      <c r="G39" s="201"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="201"/>
-      <c r="J39" s="201"/>
-      <c r="K39" s="201"/>
-      <c r="L39" s="201"/>
-      <c r="M39" s="201"/>
-      <c r="N39" s="201"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="201"/>
-      <c r="D40" s="201"/>
-      <c r="E40" s="201"/>
-      <c r="F40" s="201"/>
-      <c r="G40" s="201"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="201"/>
-      <c r="J40" s="201"/>
-      <c r="K40" s="201"/>
-      <c r="L40" s="201"/>
-      <c r="M40" s="201"/>
-      <c r="N40" s="201"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="201"/>
-      <c r="D41" s="201"/>
-      <c r="E41" s="201"/>
-      <c r="F41" s="201"/>
-      <c r="G41" s="201"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="201"/>
-      <c r="J41" s="201"/>
-      <c r="K41" s="201"/>
-      <c r="L41" s="201"/>
-      <c r="M41" s="201"/>
-      <c r="N41" s="201"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="201"/>
-      <c r="D42" s="201"/>
-      <c r="E42" s="201"/>
-      <c r="F42" s="201"/>
-      <c r="G42" s="201"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="201"/>
-      <c r="J42" s="201"/>
-      <c r="K42" s="201"/>
-      <c r="L42" s="201"/>
-      <c r="M42" s="201"/>
-      <c r="N42" s="201"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="201"/>
-      <c r="D43" s="201"/>
-      <c r="E43" s="201"/>
-      <c r="F43" s="201"/>
-      <c r="G43" s="201"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="201"/>
-      <c r="J43" s="201"/>
-      <c r="K43" s="201"/>
-      <c r="L43" s="201"/>
-      <c r="M43" s="201"/>
-      <c r="N43" s="201"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="201"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
-      <c r="F44" s="201"/>
-      <c r="G44" s="201"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="201"/>
-      <c r="J44" s="201"/>
-      <c r="K44" s="201"/>
-      <c r="L44" s="201"/>
-      <c r="M44" s="201"/>
-      <c r="N44" s="201"/>
+      <c r="D39" s="193"/>
+      <c r="E39" s="193"/>
+      <c r="F39" s="193"/>
+      <c r="G39" s="193"/>
+      <c r="H39" s="193"/>
+      <c r="I39" s="193"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="193"/>
+      <c r="L39" s="193"/>
+      <c r="M39" s="193"/>
+      <c r="N39" s="193"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="193"/>
+      <c r="D40" s="193"/>
+      <c r="E40" s="193"/>
+      <c r="F40" s="193"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
+      <c r="K40" s="193"/>
+      <c r="L40" s="193"/>
+      <c r="M40" s="193"/>
+      <c r="N40" s="193"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="193"/>
+      <c r="D41" s="193"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="193"/>
+      <c r="G41" s="193"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
+      <c r="K41" s="193"/>
+      <c r="L41" s="193"/>
+      <c r="M41" s="193"/>
+      <c r="N41" s="193"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="193"/>
+      <c r="D42" s="193"/>
+      <c r="E42" s="193"/>
+      <c r="F42" s="193"/>
+      <c r="G42" s="193"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="193"/>
+      <c r="M42" s="193"/>
+      <c r="N42" s="193"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="193"/>
+      <c r="D43" s="193"/>
+      <c r="E43" s="193"/>
+      <c r="F43" s="193"/>
+      <c r="G43" s="193"/>
+      <c r="H43" s="193"/>
+      <c r="I43" s="193"/>
+      <c r="J43" s="193"/>
+      <c r="K43" s="193"/>
+      <c r="L43" s="193"/>
+      <c r="M43" s="193"/>
+      <c r="N43" s="193"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="193"/>
+      <c r="D44" s="193"/>
+      <c r="E44" s="193"/>
+      <c r="F44" s="193"/>
+      <c r="G44" s="193"/>
+      <c r="H44" s="193"/>
+      <c r="I44" s="193"/>
+      <c r="J44" s="193"/>
+      <c r="K44" s="193"/>
+      <c r="L44" s="193"/>
+      <c r="M44" s="193"/>
+      <c r="N44" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4659,6 +4614,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4668,17 +4629,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="119" t="s">
         <v>80</v>
       </c>
@@ -4696,7 +4657,7 @@
       </c>
       <c r="J3" s="235"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="119"/>
       <c r="C4" s="119"/>
       <c r="E4" s="119"/>
@@ -4704,7 +4665,7 @@
       <c r="I4" s="234"/>
       <c r="J4" s="235"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="119">
         <v>1</v>
       </c>
@@ -4725,7 +4686,7 @@
       </c>
       <c r="J5" s="233"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="119">
         <v>1</v>
       </c>
@@ -4745,7 +4706,7 @@
       </c>
       <c r="J6" s="233"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="119">
         <v>1</v>
       </c>
@@ -4765,7 +4726,7 @@
       </c>
       <c r="J7" s="233"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="119">
         <v>2</v>
       </c>
@@ -4786,7 +4747,7 @@
       </c>
       <c r="J8" s="233"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="120">
         <v>2</v>
       </c>
@@ -4807,7 +4768,7 @@
       </c>
       <c r="J9" s="233"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="120">
         <v>2</v>
       </c>
@@ -4828,7 +4789,7 @@
       </c>
       <c r="J10" s="233"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="120">
         <v>2</v>
       </c>
@@ -4849,7 +4810,7 @@
       </c>
       <c r="J11" s="233"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="120">
         <v>3</v>
       </c>
@@ -4870,7 +4831,7 @@
       </c>
       <c r="J12" s="233"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="119">
         <v>3</v>
       </c>
@@ -4890,7 +4851,7 @@
       </c>
       <c r="J13" s="233"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="120">
         <v>3</v>
       </c>
@@ -4912,7 +4873,7 @@
       </c>
       <c r="J14" s="233"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="120">
         <v>3</v>
       </c>
@@ -4934,7 +4895,7 @@
       </c>
       <c r="J15" s="233"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="119">
         <v>4</v>
       </c>
@@ -4956,7 +4917,7 @@
       </c>
       <c r="J16" s="233"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="120">
         <v>4</v>
       </c>
@@ -4978,7 +4939,7 @@
       </c>
       <c r="J17" s="233"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="119">
         <v>4</v>
       </c>
@@ -5000,7 +4961,7 @@
       </c>
       <c r="J18" s="233"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="120">
         <v>4</v>
       </c>
@@ -5022,7 +4983,7 @@
       </c>
       <c r="J19" s="233"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="119"/>
       <c r="C20" s="119"/>
       <c r="E20" s="119"/>
@@ -5030,7 +4991,7 @@
       <c r="I20" s="232"/>
       <c r="J20" s="233"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="143" t="s">
         <v>120</v>
       </c>
@@ -5051,7 +5012,7 @@
       </c>
       <c r="J21" s="233"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="119" t="s">
         <v>86</v>
       </c>
@@ -5070,7 +5031,7 @@
       </c>
       <c r="J22" s="233"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="119" t="s">
         <v>86</v>
       </c>
@@ -5089,7 +5050,7 @@
       </c>
       <c r="J23" s="233"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="119" t="s">
         <v>86</v>
       </c>
@@ -5109,7 +5070,7 @@
       </c>
       <c r="J24" s="233"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="119" t="s">
         <v>86</v>
       </c>
@@ -5129,7 +5090,7 @@
       </c>
       <c r="J25" s="233"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="119" t="s">
         <v>86</v>
       </c>
@@ -5149,7 +5110,7 @@
       </c>
       <c r="J26" s="233"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="119" t="s">
         <v>86</v>
       </c>
@@ -5168,7 +5129,7 @@
       </c>
       <c r="J27" s="233"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="119" t="s">
         <v>86</v>
       </c>
@@ -5188,7 +5149,7 @@
       </c>
       <c r="J28" s="233"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="119" t="s">
         <v>86</v>
       </c>
@@ -5208,7 +5169,7 @@
       </c>
       <c r="J29" s="233"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="148" t="s">
         <v>120</v>
       </c>
@@ -5229,7 +5190,7 @@
       </c>
       <c r="J30" s="233"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="126"/>
       <c r="G31" s="123"/>
       <c r="I31" s="232">
@@ -5238,13 +5199,13 @@
       </c>
       <c r="J31" s="233"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="124"/>
       <c r="G32" s="125"/>
       <c r="I32" s="232"/>
       <c r="J32" s="233"/>
     </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="126">
         <f>E30+E21</f>
         <v>224896.83000000002</v>
@@ -5261,21 +5222,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5292,6 +5238,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
@@ -5301,7 +5262,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
